--- a/processing26/resultsTable_BOOM.xlsx
+++ b/processing26/resultsTable_BOOM.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2195" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2961" uniqueCount="58">
   <si>
     <t>fname</t>
   </si>
@@ -160,6 +160,33 @@
   </si>
   <si>
     <t>20260408b_arrWork.c1.nc</t>
+  </si>
+  <si>
+    <t>20260624_arr.c10.nc</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>389</t>
+  </si>
+  <si>
+    <t>20260626_arr.c10.nc</t>
+  </si>
+  <si>
+    <t>464</t>
+  </si>
+  <si>
+    <t>597</t>
+  </si>
+  <si>
+    <t>555</t>
+  </si>
+  <si>
+    <t>391</t>
+  </si>
+  <si>
+    <t>465</t>
   </si>
 </sst>
 </file>
@@ -205,13 +232,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z25"/>
+  <dimension ref="A1:Z41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" customWidth="true"/>
+    <col min="1" max="1" width="19.7109375" customWidth="true"/>
     <col min="2" max="2" width="8.85546875" customWidth="true"/>
-    <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" customWidth="true"/>
+    <col min="3" max="3" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
     <col min="6" max="6" width="16.42578125" customWidth="true"/>
     <col min="7" max="7" width="16.42578125" customWidth="true"/>
@@ -220,18 +247,18 @@
     <col min="10" max="10" width="16.42578125" customWidth="true"/>
     <col min="11" max="11" width="16.42578125" customWidth="true"/>
     <col min="12" max="12" width="12.7109375" customWidth="true"/>
-    <col min="13" max="13" width="12.7109375" customWidth="true"/>
-    <col min="14" max="14" width="12.7109375" customWidth="true"/>
-    <col min="15" max="15" width="15.42578125" customWidth="true"/>
+    <col min="13" max="13" width="13.7109375" customWidth="true"/>
+    <col min="14" max="14" width="13.7109375" customWidth="true"/>
+    <col min="15" max="15" width="16.42578125" customWidth="true"/>
     <col min="16" max="16" width="15.42578125" customWidth="true"/>
     <col min="17" max="17" width="15.7109375" customWidth="true"/>
     <col min="18" max="18" width="13.7109375" customWidth="true"/>
     <col min="19" max="19" width="13.7109375" customWidth="true"/>
     <col min="20" max="20" width="13.7109375" customWidth="true"/>
-    <col min="21" max="21" width="16.42578125" customWidth="true"/>
+    <col min="21" max="21" width="15.7109375" customWidth="true"/>
     <col min="22" max="22" width="14.7109375" customWidth="true"/>
     <col min="23" max="23" width="14.7109375" customWidth="true"/>
-    <col min="24" max="24" width="12.42578125" customWidth="true"/>
+    <col min="24" max="24" width="14.42578125" customWidth="true"/>
     <col min="25" max="25" width="13.42578125" customWidth="true"/>
     <col min="26" max="26" width="13.42578125" customWidth="true"/>
   </cols>
@@ -318,1252 +345,1306 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C2" s="0">
-        <v>0.013948657427951604</v>
+        <v>0.014146962156323427</v>
       </c>
       <c r="D2" s="0">
-        <v>0.017453292499609536</v>
+        <v>0.017453292503228274</v>
       </c>
       <c r="E2" s="0">
-        <v>0.020957927571267469</v>
+        <v>0.020759622850133122</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.002937886313870779</v>
+        <v>-0.0036185131531858215</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.0026985599028262388</v>
+        <v>-0.0033916786406752646</v>
       </c>
       <c r="H2" s="0">
-        <v>-0.0024592334917816986</v>
+        <v>-0.0031648441281647076</v>
       </c>
       <c r="I2" s="0">
-        <v>-0.0022132046668036729</v>
+        <v>-0.0021004598394360062</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.0019766542948771726</v>
+        <v>-0.0018762622255221195</v>
       </c>
       <c r="K2" s="0">
-        <v>-0.0017401039229506721</v>
+        <v>-0.001652064611608233</v>
       </c>
       <c r="L2" s="0">
-        <v>0.77594639633752582</v>
+        <v>0.76646052895346073</v>
       </c>
       <c r="M2" s="0">
-        <v>0.78175133532792263</v>
+        <v>0.77185196218046426</v>
       </c>
       <c r="N2" s="0">
-        <v>0.78755627431831943</v>
+        <v>0.77724339540746779</v>
       </c>
       <c r="O2" s="0">
-        <v>-0.02632552834749775</v>
+        <v>-0.028143684800771722</v>
       </c>
       <c r="P2" s="0">
-        <v>-0.025608895073956833</v>
+        <v>-0.027464039428544036</v>
       </c>
       <c r="Q2" s="0">
-        <v>-0.024892261800415917</v>
+        <v>-0.026784394056316351</v>
       </c>
       <c r="R2" s="0">
-        <v>0.79889966504245724</v>
+        <v>0.78237514986896439</v>
       </c>
       <c r="S2" s="0">
-        <v>0.81238248072608554</v>
+        <v>0.79497329893979873</v>
       </c>
       <c r="T2" s="0">
-        <v>0.82586529640971384</v>
+        <v>0.80757144801063308</v>
       </c>
       <c r="U2" s="0">
-        <v>0.0032158874131785497</v>
+        <v>0.0029779077935424849</v>
       </c>
       <c r="V2" s="0">
-        <v>0.0037944263105793258</v>
+        <v>0.0035205880460173092</v>
       </c>
       <c r="W2" s="0">
-        <v>0.0043729652079801014</v>
+        <v>0.004063268298492133</v>
       </c>
       <c r="X2" s="0">
-        <v>-5.0586332295676835</v>
+        <v>-1.4772803248497901</v>
       </c>
       <c r="Y2" s="0">
-        <v>-5.0447613541844589</v>
+        <v>-1.4641965042830616</v>
       </c>
       <c r="Z2" s="0">
-        <v>-5.0308894788012344</v>
+        <v>-1.4511126837163331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C3" s="0">
-        <v>0.013309613869268355</v>
+        <v>0.013712380070273259</v>
       </c>
       <c r="D3" s="0">
-        <v>0.017453292508344428</v>
+        <v>0.017453292519371524</v>
       </c>
       <c r="E3" s="0">
-        <v>0.021596971147420499</v>
+        <v>0.021194204968469788</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.0012859500781924609</v>
+        <v>-0.0012550218234771955</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.0010153984761985151</v>
+        <v>-0.0010095168469425788</v>
       </c>
       <c r="H3" s="0">
-        <v>-0.00074484687420456948</v>
+        <v>-0.00076401187040796206</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.00063204872814472623</v>
+        <v>-0.00042246552596252697</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.00036679992823318515</v>
+        <v>-0.00018180498862313771</v>
       </c>
       <c r="K3" s="0">
-        <v>-0.00010155112832164407</v>
+        <v>5.8855548716251545e-05</v>
       </c>
       <c r="L3" s="0">
-        <v>0.77403660364455318</v>
+        <v>0.75988455690536194</v>
       </c>
       <c r="M3" s="0">
-        <v>0.78080740231115497</v>
+        <v>0.76587831150611485</v>
       </c>
       <c r="N3" s="0">
-        <v>0.78757820097775677</v>
+        <v>0.77187206610686776</v>
       </c>
       <c r="O3" s="0">
-        <v>-0.024098353661426746</v>
+        <v>-0.024075903386507534</v>
       </c>
       <c r="P3" s="0">
-        <v>-0.023290048305809094</v>
+        <v>-0.023343123304146181</v>
       </c>
       <c r="Q3" s="0">
-        <v>-0.022481742950191442</v>
+        <v>-0.022610343221784828</v>
       </c>
       <c r="R3" s="0">
-        <v>0.70801822472161013</v>
+        <v>0.70577397857361668</v>
       </c>
       <c r="S3" s="0">
-        <v>0.7226788561580435</v>
+        <v>0.71889795928603362</v>
       </c>
       <c r="T3" s="0">
-        <v>0.73733948759447687</v>
+        <v>0.73202193999845056</v>
       </c>
       <c r="U3" s="0">
-        <v>0.0028606109457724807</v>
+        <v>0.0028058172250759687</v>
       </c>
       <c r="V3" s="0">
-        <v>0.0035199279787753771</v>
+        <v>0.0034033984580793932</v>
       </c>
       <c r="W3" s="0">
-        <v>0.0041792450117782735</v>
+        <v>0.0040009796910828177</v>
       </c>
       <c r="X3" s="0">
-        <v>-5.0038083718310569</v>
+        <v>-1.2253791294017029</v>
       </c>
       <c r="Y3" s="0">
-        <v>-4.9877606897787459</v>
+        <v>-1.2108749031760342</v>
       </c>
       <c r="Z3" s="0">
-        <v>-4.9717130077264349</v>
+        <v>-1.1963706769503655</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C4" s="0">
-        <v>0.0020384262988475555</v>
+        <v>0.0014346650363941584</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0074225801067767088</v>
+        <v>0.0067159720421739464</v>
       </c>
       <c r="E4" s="0">
-        <v>0.012806733914705862</v>
+        <v>0.011997279047953734</v>
       </c>
       <c r="F4" s="0">
-        <v>0.016101168850975817</v>
+        <v>0.016120171596803581</v>
       </c>
       <c r="G4" s="0">
-        <v>0.017453292396844899</v>
+        <v>0.017453292518065655</v>
       </c>
       <c r="H4" s="0">
-        <v>0.018805415942713982</v>
+        <v>0.018786413439327729</v>
       </c>
       <c r="I4" s="0">
-        <v>0.022823649646153223</v>
+        <v>0.0094758526212839808</v>
       </c>
       <c r="J4" s="0">
-        <v>0.028132462918619674</v>
+        <v>0.014527650217994192</v>
       </c>
       <c r="K4" s="0">
-        <v>0.033441276191086125</v>
+        <v>0.019579447814704401</v>
       </c>
       <c r="L4" s="0">
-        <v>0.4391231883963278</v>
+        <v>0.46144110585872172</v>
       </c>
       <c r="M4" s="0">
-        <v>0.5310416645178867</v>
+        <v>0.55041788609077669</v>
       </c>
       <c r="N4" s="0">
-        <v>0.6229601406394456</v>
+        <v>0.6393946663228316</v>
       </c>
       <c r="O4" s="0">
-        <v>0.025988826939071091</v>
+        <v>0.023645998618480907</v>
       </c>
       <c r="P4" s="0">
-        <v>0.03412047096963991</v>
+        <v>0.031682447490287362</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.042252115000208729</v>
+        <v>0.039718896362093817</v>
       </c>
       <c r="R4" s="0">
-        <v>0.73370494903434946</v>
+        <v>0.70873155377195085</v>
       </c>
       <c r="S4" s="0">
-        <v>0.74414362558688052</v>
+        <v>0.71900208247955</v>
       </c>
       <c r="T4" s="0">
-        <v>0.75458230213941158</v>
+        <v>0.72927261118714915</v>
       </c>
       <c r="U4" s="0">
-        <v>-0.00031081458619803756</v>
+        <v>-0.0013944130058633735</v>
       </c>
       <c r="V4" s="0">
-        <v>0.0023350299198718534</v>
+        <v>0.0012227333163152834</v>
       </c>
       <c r="W4" s="0">
-        <v>0.0049808744259417443</v>
+        <v>0.00383987963849394</v>
       </c>
       <c r="X4" s="0">
-        <v>-15.811108410896829</v>
+        <v>-14.051147403639416</v>
       </c>
       <c r="Y4" s="0">
-        <v>-14.387223433739205</v>
+        <v>-12.75760213452595</v>
       </c>
       <c r="Z4" s="0">
-        <v>-12.963338456581582</v>
+        <v>-11.464056865412484</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.010010182531739169</v>
+        <v>-0.010589843194010084</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0024574239044129103</v>
+        <v>0.0021925293406471818</v>
       </c>
       <c r="E5" s="0">
-        <v>0.014925030340564992</v>
+        <v>0.014974901875304446</v>
       </c>
       <c r="F5" s="0">
-        <v>0.013478033025195478</v>
+        <v>0.0142457045364672</v>
       </c>
       <c r="G5" s="0">
-        <v>0.016611986288103856</v>
+        <v>0.017453292334550528</v>
       </c>
       <c r="H5" s="0">
-        <v>0.019745939551012233</v>
+        <v>0.020660880132633858</v>
       </c>
       <c r="I5" s="0">
-        <v>-0.01684820417153499</v>
+        <v>-0.024264469615234118</v>
       </c>
       <c r="J5" s="0">
-        <v>-0.0062397161306523416</v>
+        <v>-0.013437585771764352</v>
       </c>
       <c r="K5" s="0">
-        <v>0.0043687719102303074</v>
+        <v>-0.002610701928294587</v>
       </c>
       <c r="L5" s="0">
-        <v>0.56138776085268405</v>
+        <v>0.51132824789157438</v>
       </c>
       <c r="M5" s="0">
-        <v>0.77444441278373577</v>
+        <v>0.72491239014119346</v>
       </c>
       <c r="N5" s="0">
-        <v>0.98750106471478749</v>
+        <v>0.93849653239081254</v>
       </c>
       <c r="O5" s="0">
-        <v>-0.0015716451308502109</v>
+        <v>0.0023321775960039315</v>
       </c>
       <c r="P5" s="0">
-        <v>0.015316914253864703</v>
+        <v>0.019638905010493868</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.032205473638579618</v>
+        <v>0.036945632424983804</v>
       </c>
       <c r="R5" s="0">
-        <v>0.65172048647254666</v>
+        <v>0.63223932597480348</v>
       </c>
       <c r="S5" s="0">
-        <v>0.66985107680334466</v>
+        <v>0.65063192576128792</v>
       </c>
       <c r="T5" s="0">
-        <v>0.68798166713414266</v>
+        <v>0.66902452554777237</v>
       </c>
       <c r="U5" s="0">
-        <v>-0.0031228722395326355</v>
+        <v>-0.0050655704005983298</v>
       </c>
       <c r="V5" s="0">
-        <v>0.0039339530002159943</v>
+        <v>0.0022047904825178493</v>
       </c>
       <c r="W5" s="0">
-        <v>0.010990778239964624</v>
+        <v>0.0094751513656340276</v>
       </c>
       <c r="X5" s="0">
-        <v>-10.681910422505348</v>
+        <v>-8.1986945895873493</v>
       </c>
       <c r="Y5" s="0">
-        <v>-8.323403116191022</v>
+        <v>-5.8614608116660136</v>
       </c>
       <c r="Z5" s="0">
-        <v>-5.9648958098766958</v>
+        <v>-3.5242270337446784</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C6" s="0">
-        <v>0.015387820649723239</v>
+        <v>0.015940031093601963</v>
       </c>
       <c r="D6" s="0">
-        <v>0.0174532925199078</v>
+        <v>0.017453292517519488</v>
       </c>
       <c r="E6" s="0">
-        <v>0.019518764390092362</v>
+        <v>0.018966553941437012</v>
       </c>
       <c r="F6" s="0">
-        <v>0.00036817955334520776</v>
+        <v>0.00024188851581162751</v>
       </c>
       <c r="G6" s="0">
-        <v>0.00050546420354583531</v>
+        <v>0.00034280048925158319</v>
       </c>
       <c r="H6" s="0">
-        <v>0.00064274885374646291</v>
+        <v>0.00044371246269153886</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.00090592024694081995</v>
+        <v>-0.00069409360279343714</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.00076878836048285587</v>
+        <v>-0.00059329456254637544</v>
       </c>
       <c r="K6" s="0">
-        <v>-0.00063165647402489179</v>
+        <v>-0.00049249552229931374</v>
       </c>
       <c r="L6" s="0">
-        <v>0.8449211988588653</v>
+        <v>0.83314036111762968</v>
       </c>
       <c r="M6" s="0">
-        <v>0.84928672435457897</v>
+        <v>0.83627794863430061</v>
       </c>
       <c r="N6" s="0">
-        <v>0.85365224985029264</v>
+        <v>0.83941553615097153</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.020462962792295078</v>
+        <v>-0.020970475775603056</v>
       </c>
       <c r="P6" s="0">
-        <v>-0.019995863772198148</v>
+        <v>-0.020627329883983088</v>
       </c>
       <c r="Q6" s="0">
-        <v>-0.019528764752101219</v>
+        <v>-0.02028418399236312</v>
       </c>
       <c r="R6" s="0">
-        <v>0.78402768187700978</v>
+        <v>0.77322664886321768</v>
       </c>
       <c r="S6" s="0">
-        <v>0.78923741827754135</v>
+        <v>0.77700455254834555</v>
       </c>
       <c r="T6" s="0">
-        <v>0.79444715467807292</v>
+        <v>0.78078245623347342</v>
       </c>
       <c r="U6" s="0">
-        <v>0.0047933997213672934</v>
+        <v>0.004783071648243405</v>
       </c>
       <c r="V6" s="0">
-        <v>0.0051518154585214861</v>
+        <v>0.0050457722178078174</v>
       </c>
       <c r="W6" s="0">
-        <v>0.0055102311956756788</v>
+        <v>0.0053084727873722298</v>
       </c>
       <c r="X6" s="0">
-        <v>-4.913250030240941</v>
+        <v>-1.3813947869942187</v>
       </c>
       <c r="Y6" s="0">
-        <v>-4.9047840239160809</v>
+        <v>-1.3752023252858958</v>
       </c>
       <c r="Z6" s="0">
-        <v>-4.8963180175912209</v>
+        <v>-1.3690098635775729</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C7" s="0">
-        <v>0.006184681904769453</v>
+        <v>-0.0035913089601096806</v>
       </c>
       <c r="D7" s="0">
-        <v>0.010219114202352563</v>
+        <v>0.00091164409224500057</v>
       </c>
       <c r="E7" s="0">
-        <v>0.014253546499935673</v>
+        <v>0.0054145971445996813</v>
       </c>
       <c r="F7" s="0">
-        <v>0.0019770698138932286</v>
+        <v>0.0040940230024478419</v>
       </c>
       <c r="G7" s="0">
-        <v>0.0033061030674676533</v>
+        <v>0.0052533358991590975</v>
       </c>
       <c r="H7" s="0">
-        <v>0.0046351363210420781</v>
+        <v>0.0064126487958703531</v>
       </c>
       <c r="I7" s="0">
-        <v>0.0089131023907188488</v>
+        <v>-0.0011972089590181383</v>
       </c>
       <c r="J7" s="0">
-        <v>0.012441466268947684</v>
+        <v>0.002883135259828102</v>
       </c>
       <c r="K7" s="0">
-        <v>0.015969830147176518</v>
+        <v>0.0069634794786743422</v>
       </c>
       <c r="L7" s="0">
-        <v>0.65083966949436622</v>
+        <v>0.7035377654362035</v>
       </c>
       <c r="M7" s="0">
-        <v>0.73057635736752402</v>
+        <v>0.79800788775992226</v>
       </c>
       <c r="N7" s="0">
-        <v>0.81031304524068182</v>
+        <v>0.89247801008364103</v>
       </c>
       <c r="O7" s="0">
-        <v>-0.019223641523590174</v>
+        <v>-0.018824777813896562</v>
       </c>
       <c r="P7" s="0">
-        <v>-0.013226735183276247</v>
+        <v>-0.011805908779945876</v>
       </c>
       <c r="Q7" s="0">
-        <v>-0.0072298288429623178</v>
+        <v>-0.0047870397459951909</v>
       </c>
       <c r="R7" s="0">
-        <v>0.79531077835874875</v>
+        <v>0.7793575819303421</v>
       </c>
       <c r="S7" s="0">
-        <v>0.80180948284600007</v>
+        <v>0.78710165683736399</v>
       </c>
       <c r="T7" s="0">
-        <v>0.80830818733325138</v>
+        <v>0.79484573174438589</v>
       </c>
       <c r="U7" s="0">
-        <v>0.0091793300134002595</v>
+        <v>0.0014626565158766549</v>
       </c>
       <c r="V7" s="0">
-        <v>0.012095922900977359</v>
+        <v>0.0037281953490427336</v>
       </c>
       <c r="W7" s="0">
-        <v>0.015012515788554458</v>
+        <v>0.0059937341822088128</v>
       </c>
       <c r="X7" s="0">
-        <v>-1.4353552246128529</v>
+        <v>5.082102420582407</v>
       </c>
       <c r="Y7" s="0">
-        <v>-0.7599836000559973</v>
+        <v>6.2984999219244084</v>
       </c>
       <c r="Z7" s="0">
-        <v>-0.084611975499141678</v>
+        <v>7.5148974232664099</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="0"/>
-      <c r="B8" s="0"/>
-      <c r="C8" s="0"/>
-      <c r="D8" s="0"/>
-      <c r="E8" s="0"/>
-      <c r="F8" s="0"/>
-      <c r="G8" s="0"/>
-      <c r="H8" s="0"/>
-      <c r="I8" s="0"/>
-      <c r="J8" s="0"/>
-      <c r="K8" s="0"/>
-      <c r="L8" s="0"/>
-      <c r="M8" s="0"/>
-      <c r="N8" s="0"/>
-      <c r="O8" s="0"/>
-      <c r="P8" s="0"/>
-      <c r="Q8" s="0"/>
-      <c r="R8" s="0"/>
-      <c r="S8" s="0"/>
-      <c r="T8" s="0"/>
-      <c r="U8" s="0"/>
-      <c r="V8" s="0"/>
-      <c r="W8" s="0"/>
-      <c r="X8" s="0"/>
-      <c r="Y8" s="0"/>
-      <c r="Z8" s="0"/>
+      <c r="A8" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="0">
+        <v>0.0072015190521259043</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.01113056524366411</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0.015059611435202316</v>
+      </c>
+      <c r="F8" s="0">
+        <v>0.0022172938011408095</v>
+      </c>
+      <c r="G8" s="0">
+        <v>0.0035073756775473356</v>
+      </c>
+      <c r="H8" s="0">
+        <v>0.0047974575539538617</v>
+      </c>
+      <c r="I8" s="0">
+        <v>0.0067586558069405757</v>
+      </c>
+      <c r="J8" s="0">
+        <v>0.010194744377019432</v>
+      </c>
+      <c r="K8" s="0">
+        <v>0.013630832947098288</v>
+      </c>
+      <c r="L8" s="0">
+        <v>0.61161137400519461</v>
+      </c>
+      <c r="M8" s="0">
+        <v>0.68757336450754725</v>
+      </c>
+      <c r="N8" s="0">
+        <v>0.76353535500989989</v>
+      </c>
+      <c r="O8" s="0">
+        <v>-0.016803351754257661</v>
+      </c>
+      <c r="P8" s="0">
+        <v>-0.010969550906752133</v>
+      </c>
+      <c r="Q8" s="0">
+        <v>-0.0051357500592466056</v>
+      </c>
+      <c r="R8" s="0">
+        <v>0.78228113911267783</v>
+      </c>
+      <c r="S8" s="0">
+        <v>0.78848606830238588</v>
+      </c>
+      <c r="T8" s="0">
+        <v>0.79469099749209393</v>
+      </c>
+      <c r="U8" s="0">
+        <v>0.0088424713742578601</v>
+      </c>
+      <c r="V8" s="0">
+        <v>0.011677423442556165</v>
+      </c>
+      <c r="W8" s="0">
+        <v>0.014512375510854469</v>
+      </c>
+      <c r="X8" s="0">
+        <v>1.6613267613825753</v>
+      </c>
+      <c r="Y8" s="0">
+        <v>2.309467307093481</v>
+      </c>
+      <c r="Z8" s="0">
+        <v>2.9576078528043865</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="0"/>
+        <v>49</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>55</v>
+      </c>
       <c r="C9" s="0">
-        <v>0.0068098362698035056</v>
+        <v>0.0011117722360930917</v>
       </c>
       <c r="D9" s="0">
-        <v>0.012076499290233992</v>
+        <v>0.004211180973771606</v>
       </c>
       <c r="E9" s="0">
-        <v>0.017343162310664472</v>
+        <v>0.0073105897114501203</v>
       </c>
       <c r="F9" s="0">
-        <v>0.004616769141891082</v>
+        <v>-0.0040250371506970872</v>
       </c>
       <c r="G9" s="0">
-        <v>0.0056938145961562487</v>
+        <v>-0.0038508390475124519</v>
       </c>
       <c r="H9" s="0">
-        <v>0.0067708600504214145</v>
+        <v>-0.0036766409443278166</v>
       </c>
       <c r="I9" s="0">
-        <v>0.0018562290372413106</v>
+        <v>-0.00078939963021259943</v>
       </c>
       <c r="J9" s="0">
-        <v>0.0052036617455536336</v>
+        <v>-0.00061081084623895428</v>
       </c>
       <c r="K9" s="0">
-        <v>0.0085510944538659574</v>
+        <v>-0.00043222206226530913</v>
       </c>
       <c r="L9" s="0">
-        <v>0.67437580293072041</v>
+        <v>0.69376139921899915</v>
       </c>
       <c r="M9" s="0">
-        <v>0.7413179827771339</v>
+        <v>0.71561817826478691</v>
       </c>
       <c r="N9" s="0">
-        <v>0.80826016262354727</v>
+        <v>0.73747495731057466</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.010948884086098143</v>
+        <v>-0.026318155168569446</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.0054473595186226185</v>
+        <v>-0.024089547326642199</v>
       </c>
       <c r="Q9" s="0">
-        <v>5.4165048852908671e-05</v>
+        <v>-0.021860939484714952</v>
       </c>
       <c r="R9" s="0">
-        <v>0.74528029758445369</v>
+        <v>0.7751948738341814</v>
       </c>
       <c r="S9" s="0">
-        <v>0.75668382339964924</v>
+        <v>0.77993618814900179</v>
       </c>
       <c r="T9" s="0">
-        <v>0.76808734921484501</v>
+        <v>0.78467750246382218</v>
       </c>
       <c r="U9" s="0">
-        <v>0.002769256877997985</v>
+        <v>0.0072628685658414687</v>
       </c>
       <c r="V9" s="0">
-        <v>0.0051385125948235659</v>
+        <v>0.0077304570170477552</v>
       </c>
       <c r="W9" s="0">
-        <v>0.0075077683116491463</v>
+        <v>0.0081980454682540425</v>
       </c>
       <c r="X9" s="0">
-        <v>-7.1506776149424516</v>
+        <v>-1.0872102315282393</v>
       </c>
       <c r="Y9" s="0">
-        <v>-6.4013193696442512</v>
+        <v>-1.0747468765495132</v>
       </c>
       <c r="Z9" s="0">
-        <v>-5.6519611243460517</v>
+        <v>-1.0622835215707871</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="0"/>
+        <v>49</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>55</v>
+      </c>
       <c r="C10" s="0">
-        <v>0.0097248331190615614</v>
+        <v>0.013245180727763864</v>
       </c>
       <c r="D10" s="0">
-        <v>0.0063932021768487255</v>
+        <v>0.015175288245123427</v>
       </c>
       <c r="E10" s="0">
-        <v>0.00379122493638452</v>
+        <v>0.017105395762482989</v>
       </c>
       <c r="F10" s="0">
-        <v>0.0080913147703958379</v>
+        <v>0.0005405551101994782</v>
       </c>
       <c r="G10" s="0">
-        <v>0.0090061915054244317</v>
+        <v>0.00063832120228313302</v>
       </c>
       <c r="H10" s="0">
-        <v>0.0099697418585749081</v>
+        <v>0.00073608729436678785</v>
       </c>
       <c r="I10" s="0">
-        <v>0.013188398657585832</v>
+        <v>0.00052936428726536584</v>
       </c>
       <c r="J10" s="0">
-        <v>0.012863310435025577</v>
+        <v>0.00062576271745211581</v>
       </c>
       <c r="K10" s="0">
-        <v>0.013835827132944931</v>
+        <v>0.00072216114763886579</v>
       </c>
       <c r="L10" s="0">
-        <v>0.15362202484751336</v>
+        <v>0.7360466260233206</v>
       </c>
       <c r="M10" s="0">
-        <v>0.10980017514879864</v>
+        <v>0.73911129612493731</v>
       </c>
       <c r="N10" s="0">
-        <v>0.11780021185728286</v>
+        <v>0.74217596622655402</v>
       </c>
       <c r="O10" s="0">
-        <v>0.02010306518585608</v>
+        <v>-0.016786855634305872</v>
       </c>
       <c r="P10" s="0">
-        <v>0.024469552491617776</v>
+        <v>-0.01636840347932025</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.029601056375140988</v>
+        <v>-0.015949951324334629</v>
       </c>
       <c r="R10" s="0">
-        <v>0.058575309450324763</v>
+        <v>0.79230055312885106</v>
       </c>
       <c r="S10" s="0">
-        <v>0.054866970661143349</v>
+        <v>0.79752888460727856</v>
       </c>
       <c r="T10" s="0">
-        <v>0.051372334845535023</v>
+        <v>0.80275721608570605</v>
       </c>
       <c r="U10" s="0">
-        <v>0.0042331558443891616</v>
+        <v>0.0064196039183972908</v>
       </c>
       <c r="V10" s="0">
-        <v>0.0035254105621579592</v>
+        <v>0.0067840731038907231</v>
       </c>
       <c r="W10" s="0">
-        <v>0.0044661840076005432</v>
+        <v>0.0071485422893841554</v>
       </c>
       <c r="X10" s="0">
-        <v>5.1793697723237591</v>
+        <v>-1.047098238658684</v>
       </c>
       <c r="Y10" s="0">
-        <v>4.5906808807985886</v>
+        <v>-1.0423696078035982</v>
       </c>
       <c r="Z10" s="0">
-        <v>4.1465408993702804</v>
+        <v>-1.0376409769485124</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="0"/>
-      <c r="B11" s="0"/>
-      <c r="C11" s="0"/>
-      <c r="D11" s="0"/>
-      <c r="E11" s="0"/>
-      <c r="F11" s="0"/>
-      <c r="G11" s="0"/>
-      <c r="H11" s="0"/>
-      <c r="I11" s="0"/>
-      <c r="J11" s="0"/>
-      <c r="K11" s="0"/>
-      <c r="L11" s="0"/>
-      <c r="M11" s="0"/>
-      <c r="N11" s="0"/>
-      <c r="O11" s="0"/>
-      <c r="P11" s="0"/>
-      <c r="Q11" s="0"/>
-      <c r="R11" s="0"/>
-      <c r="S11" s="0"/>
-      <c r="T11" s="0"/>
-      <c r="U11" s="0"/>
-      <c r="V11" s="0"/>
-      <c r="W11" s="0"/>
-      <c r="X11" s="0"/>
-      <c r="Y11" s="0"/>
-      <c r="Z11" s="0"/>
+      <c r="A11" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="0">
+        <v>0.00044283392179864968</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0.0057275106732012707</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0.011012187424603892</v>
+      </c>
+      <c r="F11" s="0">
+        <v>0.0008375839015979567</v>
+      </c>
+      <c r="G11" s="0">
+        <v>0.0032456354148865485</v>
+      </c>
+      <c r="H11" s="0">
+        <v>0.0056536869281751407</v>
+      </c>
+      <c r="I11" s="0">
+        <v>-0.042140625912414666</v>
+      </c>
+      <c r="J11" s="0">
+        <v>-0.03490658080550977</v>
+      </c>
+      <c r="K11" s="0">
+        <v>-0.027672535698604874</v>
+      </c>
+      <c r="L11" s="0">
+        <v>0.64099219731572032</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.70588565783844526</v>
+      </c>
+      <c r="N11" s="0">
+        <v>0.77077911836117019</v>
+      </c>
+      <c r="O11" s="0">
+        <v>-0.014137126578223226</v>
+      </c>
+      <c r="P11" s="0">
+        <v>-0.0069461948212483698</v>
+      </c>
+      <c r="Q11" s="0">
+        <v>0.00024473693572648735</v>
+      </c>
+      <c r="R11" s="0">
+        <v>0.76887943165025607</v>
+      </c>
+      <c r="S11" s="0">
+        <v>0.77687958948918145</v>
+      </c>
+      <c r="T11" s="0">
+        <v>0.78487974732810684</v>
+      </c>
+      <c r="U11" s="0">
+        <v>-0.0021926524836741977</v>
+      </c>
+      <c r="V11" s="0">
+        <v>0.0029650021132028295</v>
+      </c>
+      <c r="W11" s="0">
+        <v>0.0081226567100798567</v>
+      </c>
+      <c r="X11" s="0">
+        <v>-0.050615997446269656</v>
+      </c>
+      <c r="Y11" s="0">
+        <v>1.1679531675409809</v>
+      </c>
+      <c r="Z11" s="0">
+        <v>2.3865223325282314</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="0"/>
+        <v>52</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>53</v>
+      </c>
       <c r="C12" s="0">
-        <v>0.015678641248588466</v>
+        <v>0.013730315985622764</v>
       </c>
       <c r="D12" s="0">
-        <v>0.017453292519911963</v>
+        <v>0.017453242990912252</v>
       </c>
       <c r="E12" s="0">
-        <v>0.01922794379123546</v>
+        <v>0.021176169996201741</v>
       </c>
       <c r="F12" s="0">
-        <v>-0.00095379816614962092</v>
+        <v>0.0044334305368094401</v>
       </c>
       <c r="G12" s="0">
-        <v>-0.00083166635979889175</v>
+        <v>0.0046712494222237644</v>
       </c>
       <c r="H12" s="0">
-        <v>-0.00070953455344816257</v>
+        <v>0.0049090683076380886</v>
       </c>
       <c r="I12" s="0">
-        <v>-0.0015401257001548708</v>
+        <v>0.0014193079968782653</v>
       </c>
       <c r="J12" s="0">
-        <v>-0.0014181212713143814</v>
+        <v>0.0016603592748069111</v>
       </c>
       <c r="K12" s="0">
-        <v>-0.001296116842473892</v>
+        <v>0.0019014105527355568</v>
       </c>
       <c r="L12" s="0">
-        <v>0.79519359114799637</v>
+        <v>0.84191356960167818</v>
       </c>
       <c r="M12" s="0">
-        <v>0.79844785803642393</v>
+        <v>0.86142479199544364</v>
       </c>
       <c r="N12" s="0">
-        <v>0.80170212492485149</v>
+        <v>0.8809360143892091</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.022457342141524818</v>
+        <v>-0.021910073406539266</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.022079838041080682</v>
+        <v>-0.019811264423988922</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.021702333940636545</v>
+        <v>-0.017712455441438579</v>
       </c>
       <c r="R12" s="0">
-        <v>0.78152012534727611</v>
+        <v>0.76164438439774473</v>
       </c>
       <c r="S12" s="0">
-        <v>0.78641411575112141</v>
+        <v>0.76761566497391254</v>
       </c>
       <c r="T12" s="0">
-        <v>0.79130810615496672</v>
+        <v>0.77358694555008034</v>
       </c>
       <c r="U12" s="0">
-        <v>0.0045285711494369042</v>
+        <v>0.004632200839971538</v>
       </c>
       <c r="V12" s="0">
-        <v>0.004832689517453745</v>
+        <v>0.0053802653269846325</v>
       </c>
       <c r="W12" s="0">
-        <v>0.0051368078854705859</v>
+        <v>0.0061283298139977269</v>
       </c>
       <c r="X12" s="0">
-        <v>-4.9861707886482494</v>
+        <v>-1.1525174031589329</v>
       </c>
       <c r="Y12" s="0">
-        <v>-4.9787612205420917</v>
+        <v>-1.1363591491758325</v>
       </c>
       <c r="Z12" s="0">
-        <v>-4.971351652435934</v>
+        <v>-1.120200895192732</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B13" s="0" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="C13" s="0">
-        <v>0.014034799621027296</v>
+        <v>-0.0011552921531000192</v>
       </c>
       <c r="D13" s="0">
-        <v>0.017453292503075466</v>
+        <v>0.0032277997339100429</v>
       </c>
       <c r="E13" s="0">
-        <v>0.020871785385123635</v>
+        <v>0.0076108916209201051</v>
       </c>
       <c r="F13" s="0">
-        <v>-0.0029217517807173963</v>
+        <v>0.0020263774668741745</v>
       </c>
       <c r="G13" s="0">
-        <v>-0.002687899329345201</v>
+        <v>0.0022295563334521601</v>
       </c>
       <c r="H13" s="0">
-        <v>-0.0024540468779730056</v>
+        <v>0.0024327352000301458</v>
       </c>
       <c r="I13" s="0">
-        <v>-0.0021745920357787627</v>
+        <v>0.0011208942833840581</v>
       </c>
       <c r="J13" s="0">
-        <v>-0.0019434552521408474</v>
+        <v>0.0013183298101759166</v>
       </c>
       <c r="K13" s="0">
-        <v>-0.001712318468502932</v>
+        <v>0.0015157653369677752</v>
       </c>
       <c r="L13" s="0">
-        <v>0.77602604720669655</v>
+        <v>0.84379054710477375</v>
       </c>
       <c r="M13" s="0">
-        <v>0.78168741334323622</v>
+        <v>0.85044094166802309</v>
       </c>
       <c r="N13" s="0">
-        <v>0.78734877947977588</v>
+        <v>0.85709133623127243</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.026283838248328681</v>
+        <v>-0.026335609670816777</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.025584133948303504</v>
+        <v>-0.025403727598416189</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.024884429648278326</v>
+        <v>-0.024471845526015602</v>
       </c>
       <c r="R13" s="0">
-        <v>0.80062068968668787</v>
+        <v>0.75031420059098985</v>
       </c>
       <c r="S13" s="0">
-        <v>0.81379638717879865</v>
+        <v>0.7646593619792007</v>
       </c>
       <c r="T13" s="0">
-        <v>0.82697208467090944</v>
+        <v>0.77900452336741155</v>
       </c>
       <c r="U13" s="0">
-        <v>0.0032758331733373238</v>
+        <v>0.00031833678271430647</v>
       </c>
       <c r="V13" s="0">
-        <v>0.0038410217646434506</v>
+        <v>0.0011824346586787637</v>
       </c>
       <c r="W13" s="0">
-        <v>0.0044062103559495778</v>
+        <v>0.002046532534643221</v>
       </c>
       <c r="X13" s="0">
-        <v>-4.8264822202944053</v>
+        <v>-1.1274575510556144</v>
       </c>
       <c r="Y13" s="0">
-        <v>-4.8129333867415731</v>
+        <v>-1.1169726233305191</v>
       </c>
       <c r="Z13" s="0">
-        <v>-4.7993845531887409</v>
+        <v>-1.1064876956054237</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="C14" s="0">
-        <v>0.013421068242030028</v>
+        <v>0.0096645076215733112</v>
       </c>
       <c r="D14" s="0">
-        <v>0.017453292508373002</v>
+        <v>0.017453292503203183</v>
       </c>
       <c r="E14" s="0">
-        <v>0.021485516774715975</v>
+        <v>0.025242077384833056</v>
       </c>
       <c r="F14" s="0">
-        <v>-0.0012698723247649244</v>
+        <v>0.0079378849543148382</v>
       </c>
       <c r="G14" s="0">
-        <v>-0.0010062181096704356</v>
+        <v>0.0091251064932791615</v>
       </c>
       <c r="H14" s="0">
-        <v>-0.00074256389457594686</v>
+        <v>0.010312328032243485</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.00059387142723371211</v>
+        <v>-0.0019649480656246769</v>
       </c>
       <c r="J14" s="0">
-        <v>-0.00033539279777207968</v>
+        <v>-0.00079181415991542927</v>
       </c>
       <c r="K14" s="0">
-        <v>-7.6914168310447206e-05</v>
+        <v>0.00038131974579381838</v>
       </c>
       <c r="L14" s="0">
-        <v>0.77355698515366966</v>
+        <v>0.72414680763044836</v>
       </c>
       <c r="M14" s="0">
-        <v>0.78014085260561961</v>
+        <v>0.73691984706521385</v>
       </c>
       <c r="N14" s="0">
-        <v>0.78672472005756955</v>
+        <v>0.74969288649997934</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.024001829223107209</v>
+        <v>-0.00058702618212559199</v>
       </c>
       <c r="P14" s="0">
-        <v>-0.023214789031986243</v>
+        <v>0.0021351259503922509</v>
       </c>
       <c r="Q14" s="0">
-        <v>-0.022427748840865278</v>
+        <v>0.0048572780829100933</v>
       </c>
       <c r="R14" s="0">
-        <v>0.71065185678473109</v>
+        <v>0.9303826594731851</v>
       </c>
       <c r="S14" s="0">
-        <v>0.72494245538938706</v>
+        <v>0.96333871486451761</v>
       </c>
       <c r="T14" s="0">
-        <v>0.73923305399404304</v>
+        <v>0.99629477025585012</v>
       </c>
       <c r="U14" s="0">
-        <v>0.0028914703704168532</v>
+        <v>0.0085832320673474485</v>
       </c>
       <c r="V14" s="0">
-        <v>0.0035338779123592168</v>
+        <v>0.011095108936735673</v>
       </c>
       <c r="W14" s="0">
-        <v>0.0041762854543015808</v>
+        <v>0.013606985806123897</v>
       </c>
       <c r="X14" s="0">
-        <v>-4.7718696309850603</v>
+        <v>-0.56528423323677923</v>
       </c>
       <c r="Y14" s="0">
-        <v>-4.7562363615554233</v>
+        <v>-0.52643336819908981</v>
       </c>
       <c r="Z14" s="0">
-        <v>-4.7406030921257862</v>
+        <v>-0.48758250316140034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0018594609836855612</v>
+        <v>0.0021444375863865694</v>
       </c>
       <c r="D15" s="0">
-        <v>0.0073164991463882988</v>
+        <v>0.0062267983007894753</v>
       </c>
       <c r="E15" s="0">
-        <v>0.012773537309091036</v>
+        <v>0.01030915901519238</v>
       </c>
       <c r="F15" s="0">
-        <v>0.016084020803878774</v>
+        <v>-0.019881340549225898</v>
       </c>
       <c r="G15" s="0">
-        <v>0.017453292433895581</v>
+        <v>-0.017453292519268943</v>
       </c>
       <c r="H15" s="0">
-        <v>0.018822564063912389</v>
+        <v>-0.015025244489311987</v>
       </c>
       <c r="I15" s="0">
-        <v>0.022297174070805156</v>
+        <v>-0.0082338833197616451</v>
       </c>
       <c r="J15" s="0">
-        <v>0.027660577955260182</v>
+        <v>-0.0015349524344451583</v>
       </c>
       <c r="K15" s="0">
-        <v>0.033023981839715208</v>
+        <v>0.0051639784508713295</v>
       </c>
       <c r="L15" s="0">
-        <v>0.43800783049727715</v>
+        <v>0.67001119391848152</v>
       </c>
       <c r="M15" s="0">
-        <v>0.53099796601885263</v>
+        <v>0.73021728058177426</v>
       </c>
       <c r="N15" s="0">
-        <v>0.62398810154042805</v>
+        <v>0.79042336724506701</v>
       </c>
       <c r="O15" s="0">
-        <v>0.025898048812692139</v>
+        <v>-0.05639187925314236</v>
       </c>
       <c r="P15" s="0">
-        <v>0.034126635705775454</v>
+        <v>-0.049007928831723051</v>
       </c>
       <c r="Q15" s="0">
-        <v>0.042355222598858766</v>
+        <v>-0.041623978410303741</v>
       </c>
       <c r="R15" s="0">
-        <v>0.73227269471956791</v>
+        <v>0.78968623671947213</v>
       </c>
       <c r="S15" s="0">
-        <v>0.7428848137457521</v>
+        <v>0.79642218861425251</v>
       </c>
       <c r="T15" s="0">
-        <v>0.7534969327719363</v>
+        <v>0.80315814050903289</v>
       </c>
       <c r="U15" s="0">
-        <v>-0.00046768032459700015</v>
+        <v>0.0060628026087598211</v>
       </c>
       <c r="V15" s="0">
-        <v>0.0022118857650923825</v>
+        <v>0.010918043221004982</v>
       </c>
       <c r="W15" s="0">
-        <v>0.0048914518547817651</v>
+        <v>0.015773283833250142</v>
       </c>
       <c r="X15" s="0">
-        <v>-15.705989747095813</v>
+        <v>1.8087787202738051</v>
       </c>
       <c r="Y15" s="0">
-        <v>-14.268223999841924</v>
+        <v>2.8302730404694483</v>
       </c>
       <c r="Z15" s="0">
-        <v>-12.830458252588034</v>
+        <v>3.8517673606650913</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="0">
-        <v>-0.0099630788896901898</v>
-      </c>
-      <c r="D16" s="0">
-        <v>0.0024717801270845796</v>
-      </c>
-      <c r="E16" s="0">
-        <v>0.014906639143859347</v>
-      </c>
-      <c r="F16" s="0">
-        <v>0.013416090637235374</v>
-      </c>
-      <c r="G16" s="0">
-        <v>0.01654265698545351</v>
-      </c>
-      <c r="H16" s="0">
-        <v>0.019669223333671645</v>
-      </c>
-      <c r="I16" s="0">
-        <v>-0.017284588016350369</v>
-      </c>
-      <c r="J16" s="0">
-        <v>-0.0067002307635767042</v>
-      </c>
-      <c r="K16" s="0">
-        <v>0.0038841264891969598</v>
-      </c>
-      <c r="L16" s="0">
-        <v>0.56294738176220283</v>
-      </c>
-      <c r="M16" s="0">
-        <v>0.77560936704440819</v>
-      </c>
-      <c r="N16" s="0">
-        <v>0.98827135232661356</v>
-      </c>
-      <c r="O16" s="0">
-        <v>-0.0017595910015238015</v>
-      </c>
-      <c r="P16" s="0">
-        <v>0.015094881746458557</v>
-      </c>
-      <c r="Q16" s="0">
-        <v>0.031949354494440918</v>
-      </c>
-      <c r="R16" s="0">
-        <v>0.65226985482986344</v>
-      </c>
-      <c r="S16" s="0">
-        <v>0.6703525877874621</v>
-      </c>
-      <c r="T16" s="0">
-        <v>0.68843532074506075</v>
-      </c>
-      <c r="U16" s="0">
-        <v>-0.0030693712333342837</v>
-      </c>
-      <c r="V16" s="0">
-        <v>0.0039699075315653178</v>
-      </c>
-      <c r="W16" s="0">
-        <v>0.011009186296464919</v>
-      </c>
-      <c r="X16" s="0">
-        <v>-10.2741152539572</v>
-      </c>
-      <c r="Y16" s="0">
-        <v>-7.9180399476335639</v>
-      </c>
-      <c r="Z16" s="0">
-        <v>-5.5619646413099275</v>
-      </c>
+      <c r="A16" s="0"/>
+      <c r="B16" s="0"/>
+      <c r="C16" s="0"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
+      <c r="G16" s="0"/>
+      <c r="H16" s="0"/>
+      <c r="I16" s="0"/>
+      <c r="J16" s="0"/>
+      <c r="K16" s="0"/>
+      <c r="L16" s="0"/>
+      <c r="M16" s="0"/>
+      <c r="N16" s="0"/>
+      <c r="O16" s="0"/>
+      <c r="P16" s="0"/>
+      <c r="Q16" s="0"/>
+      <c r="R16" s="0"/>
+      <c r="S16" s="0"/>
+      <c r="T16" s="0"/>
+      <c r="U16" s="0"/>
+      <c r="V16" s="0"/>
+      <c r="W16" s="0"/>
+      <c r="X16" s="0"/>
+      <c r="Y16" s="0"/>
+      <c r="Z16" s="0"/>
     </row>
     <row r="17">
       <c r="A17" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>37</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="B17" s="0"/>
       <c r="C17" s="0">
-        <v>0.015544660537655649</v>
+        <v>0.0055312972271955125</v>
       </c>
       <c r="D17" s="0">
-        <v>0.017453292519907855</v>
+        <v>0.010198978691411485</v>
       </c>
       <c r="E17" s="0">
-        <v>0.019361924502160063</v>
+        <v>0.014866660155627456</v>
       </c>
       <c r="F17" s="0">
-        <v>0.00039665147899606746</v>
+        <v>0.0017082143389914961</v>
       </c>
       <c r="G17" s="0">
-        <v>0.00052367253130552462</v>
+        <v>0.0027296170521642661</v>
       </c>
       <c r="H17" s="0">
-        <v>0.00065069358361498179</v>
+        <v>0.0037510197653370372</v>
       </c>
       <c r="I17" s="0">
-        <v>-0.00086982073479495437</v>
+        <v>-0.004464534248193255</v>
       </c>
       <c r="J17" s="0">
-        <v>-0.00074294184179093947</v>
+        <v>-0.0016230802955206163</v>
       </c>
       <c r="K17" s="0">
-        <v>-0.00061606294878692458</v>
+        <v>0.0012183736571520225</v>
       </c>
       <c r="L17" s="0">
-        <v>0.8451410932520762</v>
+        <v>0.69986187721296922</v>
       </c>
       <c r="M17" s="0">
-        <v>0.84917160352956489</v>
+        <v>0.74818126745421021</v>
       </c>
       <c r="N17" s="0">
-        <v>0.85320211380705357</v>
+        <v>0.79650065769545131</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.020381971933686158</v>
+        <v>-0.017521910229305302</v>
       </c>
       <c r="P17" s="0">
-        <v>-0.019950265022301277</v>
+        <v>-0.013027181452395486</v>
       </c>
       <c r="Q17" s="0">
-        <v>-0.019518558110916396</v>
+        <v>-0.008532452675485672</v>
       </c>
       <c r="R17" s="0">
-        <v>0.78480934043533057</v>
+        <v>0.7665991227064467</v>
       </c>
       <c r="S17" s="0">
-        <v>0.7896307018795411</v>
+        <v>0.77731986691657939</v>
       </c>
       <c r="T17" s="0">
-        <v>0.79445206332375162</v>
+        <v>0.7880406111267122</v>
       </c>
       <c r="U17" s="0">
-        <v>0.0048511127165144843</v>
+        <v>0.0032498809607065964</v>
       </c>
       <c r="V17" s="0">
-        <v>0.0051827345035264198</v>
+        <v>0.0054898775492772788</v>
       </c>
       <c r="W17" s="0">
-        <v>0.0055143562905383553</v>
+        <v>0.0077298741378479625</v>
       </c>
       <c r="X17" s="0">
-        <v>-4.7431288817805077</v>
+        <v>-1.6294194276655858</v>
       </c>
       <c r="Y17" s="0">
-        <v>-4.7352977021248845</v>
+        <v>-1.0685732047833707</v>
       </c>
       <c r="Z17" s="0">
-        <v>-4.7274665224692614</v>
+        <v>-0.50772698190115506</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0" t="s">
-        <v>41</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>39</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B18" s="0"/>
       <c r="C18" s="0">
-        <v>0.00622089995559056</v>
+        <v>0.0081221633101996819</v>
       </c>
       <c r="D18" s="0">
-        <v>0.010255657506901415</v>
+        <v>0.0066301675817574731</v>
       </c>
       <c r="E18" s="0">
-        <v>0.014290415058212269</v>
+        <v>0.0061208159322584761</v>
       </c>
       <c r="F18" s="0">
-        <v>0.0019622525018809954</v>
+        <v>0.008582570121182076</v>
       </c>
       <c r="G18" s="0">
-        <v>0.003291542243440367</v>
+        <v>0.0087614096671759165</v>
       </c>
       <c r="H18" s="0">
-        <v>0.0046208319849997386</v>
+        <v>0.0090549460656955509</v>
       </c>
       <c r="I18" s="0">
-        <v>0.0083995198227418445</v>
+        <v>0.01331094599100739</v>
       </c>
       <c r="J18" s="0">
-        <v>0.011927225470586045</v>
+        <v>0.011427370846112972</v>
       </c>
       <c r="K18" s="0">
-        <v>0.015454931118430246</v>
+        <v>0.010399171550464322</v>
       </c>
       <c r="L18" s="0">
-        <v>0.65153249502169763</v>
+        <v>0.11541879309287816</v>
       </c>
       <c r="M18" s="0">
-        <v>0.73129057831031419</v>
+        <v>0.078986131707233676</v>
       </c>
       <c r="N18" s="0">
-        <v>0.81104866159893074</v>
+        <v>0.077503272615453547</v>
       </c>
       <c r="O18" s="0">
-        <v>-0.019303495484701075</v>
+        <v>0.018065772764142403</v>
       </c>
       <c r="P18" s="0">
-        <v>-0.013305103123173274</v>
+        <v>0.020264754894016381</v>
       </c>
       <c r="Q18" s="0">
-        <v>-0.0073067107616454716</v>
+        <v>0.023227662114784758</v>
       </c>
       <c r="R18" s="0">
-        <v>0.7954219089157808</v>
+        <v>0.0645635523928728</v>
       </c>
       <c r="S18" s="0">
-        <v>0.80192183993058686</v>
+        <v>0.06738742295548282</v>
       </c>
       <c r="T18" s="0">
-        <v>0.80842177094539291</v>
+        <v>0.070932277293655352</v>
       </c>
       <c r="U18" s="0">
-        <v>0.0091960715814877105</v>
+        <v>0.0042102765979939788</v>
       </c>
       <c r="V18" s="0">
-        <v>0.012113017756314461</v>
+        <v>0.0036304069066558174</v>
       </c>
       <c r="W18" s="0">
-        <v>0.015029963931141211</v>
+        <v>0.0042536861811011927</v>
       </c>
       <c r="X18" s="0">
-        <v>-1.1075701750274665</v>
+        <v>4.5584650730419547</v>
       </c>
       <c r="Y18" s="0">
-        <v>-0.43174670758029804</v>
+        <v>4.3506455057227162</v>
       </c>
       <c r="Z18" s="0">
-        <v>0.24407675986687044</v>
+        <v>4.2636365497347271</v>
       </c>
     </row>
     <row r="19">
@@ -1596,420 +1677,1646 @@
     </row>
     <row r="20">
       <c r="A20" s="0" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B20" s="0"/>
       <c r="C20" s="0">
-        <v>0.0076126759137715638</v>
+        <v>0.016326997762826989</v>
       </c>
       <c r="D20" s="0">
-        <v>0.012052386936008614</v>
+        <v>0.017453292512720132</v>
       </c>
       <c r="E20" s="0">
-        <v>0.016540741538362238</v>
+        <v>0.018579587262613277</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0044748194609328445</v>
+        <v>-0.00061550745402102103</v>
       </c>
       <c r="G20" s="0">
-        <v>0.0054765516049199098</v>
+        <v>-0.00053404276749342947</v>
       </c>
       <c r="H20" s="0">
-        <v>0.0064815286567817638</v>
+        <v>-0.00045257808096583796</v>
       </c>
       <c r="I20" s="0">
-        <v>0.0022943798598339558</v>
+        <v>-0.00060778210626074886</v>
       </c>
       <c r="J20" s="0">
-        <v>0.0051824402768768183</v>
+        <v>-0.00052618271626519476</v>
       </c>
       <c r="K20" s="0">
-        <v>0.0081570076886183229</v>
+        <v>-0.00044458332626964067</v>
       </c>
       <c r="L20" s="0">
-        <v>0.64777720462694488</v>
+        <v>0.76810417465455094</v>
       </c>
       <c r="M20" s="0">
-        <v>0.70309144623181041</v>
+        <v>0.77020157944364875</v>
       </c>
       <c r="N20" s="0">
-        <v>0.76186048026382236</v>
+        <v>0.77229898423274657</v>
       </c>
       <c r="O20" s="0">
-        <v>-0.0096552761758007012</v>
+        <v>-0.020931688792041526</v>
       </c>
       <c r="P20" s="0">
-        <v>-0.0045716383902234346</v>
+        <v>-0.02067001241048972</v>
       </c>
       <c r="Q20" s="0">
-        <v>0.00056300050053793447</v>
+        <v>-0.020408336028937914</v>
       </c>
       <c r="R20" s="0">
-        <v>0.70220692421738251</v>
+        <v>0.7678530551355468</v>
       </c>
       <c r="S20" s="0">
-        <v>0.71210644240808929</v>
+        <v>0.77055874557150006</v>
       </c>
       <c r="T20" s="0">
-        <v>0.72202020746370077</v>
+        <v>0.77326443600745332</v>
       </c>
       <c r="U20" s="0">
-        <v>0.0029882640949091361</v>
+        <v>0.0047451452960464418</v>
       </c>
       <c r="V20" s="0">
-        <v>0.0050120088984585273</v>
+        <v>0.0049550987477332232</v>
       </c>
       <c r="W20" s="0">
-        <v>0.0071456549505195055</v>
+        <v>0.0051650521994200047</v>
       </c>
       <c r="X20" s="0">
-        <v>-6.0860466820041399</v>
+        <v>-1.2560118337388191</v>
       </c>
       <c r="Y20" s="0">
-        <v>-5.4746529355153948</v>
+        <v>-1.2510956090928243</v>
       </c>
       <c r="Z20" s="0">
-        <v>-4.8536225950201937</v>
+        <v>-1.2461793844468294</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>53</v>
+      </c>
       <c r="C21" s="0">
-        <v>0.0085721139039518397</v>
+        <v>0.01414060661461727</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0057972877474292538</v>
+        <v>0.017453292503224346</v>
       </c>
       <c r="E21" s="0">
-        <v>0.0047752278902828986</v>
+        <v>0.020765978391831422</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0070478564722259284</v>
+        <v>-0.0036167666486837434</v>
       </c>
       <c r="G21" s="0">
-        <v>0.0078468859599871918</v>
+        <v>-0.0033895547808799739</v>
       </c>
       <c r="H21" s="0">
-        <v>0.0086897027425275504</v>
+        <v>-0.0031623429130762043</v>
       </c>
       <c r="I21" s="0">
-        <v>0.011537029115076362</v>
+        <v>-0.0021035549133370246</v>
       </c>
       <c r="J21" s="0">
-        <v>0.011142524086860662</v>
+        <v>-0.0018789823417485715</v>
       </c>
       <c r="K21" s="0">
-        <v>0.011987790474683324</v>
+        <v>-0.0016544097701601183</v>
       </c>
       <c r="L21" s="0">
-        <v>0.19110695921631554</v>
+        <v>0.76643595706996082</v>
       </c>
       <c r="M21" s="0">
-        <v>0.18911829288427654</v>
+        <v>0.77183823631660908</v>
       </c>
       <c r="N21" s="0">
-        <v>0.20409333999787097</v>
+        <v>0.77724051556325735</v>
       </c>
       <c r="O21" s="0">
-        <v>0.019083829043877672</v>
+        <v>-0.028139277224992168</v>
       </c>
       <c r="P21" s="0">
-        <v>0.022575725050955856</v>
+        <v>-0.027458403926543706</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.026852666197781965</v>
+        <v>-0.026777530628095243</v>
       </c>
       <c r="R21" s="0">
-        <v>0.18504077202294128</v>
+        <v>0.78246144383695526</v>
       </c>
       <c r="S21" s="0">
-        <v>0.18779175267401668</v>
+        <v>0.79507974403409676</v>
       </c>
       <c r="T21" s="0">
-        <v>0.19063086021268805</v>
+        <v>0.80769804423123826</v>
       </c>
       <c r="U21" s="0">
-        <v>0.0036311522552382107</v>
+        <v>0.0029763531310176309</v>
       </c>
       <c r="V21" s="0">
-        <v>0.0030170109550587449</v>
+        <v>0.0035199717421154669</v>
       </c>
       <c r="W21" s="0">
-        <v>0.0039007361300445569</v>
+        <v>0.004063590353213303</v>
       </c>
       <c r="X21" s="0">
-        <v>5.4127376732270944</v>
+        <v>-1.6119571128808379</v>
       </c>
       <c r="Y21" s="0">
-        <v>4.8045228662216672</v>
+        <v>-1.598847405278442</v>
       </c>
       <c r="Z21" s="0">
-        <v>4.3226731632039908</v>
+        <v>-1.5857376976760462</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="0"/>
-      <c r="B22" s="0"/>
-      <c r="C22" s="0"/>
-      <c r="D22" s="0"/>
-      <c r="E22" s="0"/>
-      <c r="F22" s="0"/>
-      <c r="G22" s="0"/>
-      <c r="H22" s="0"/>
-      <c r="I22" s="0"/>
-      <c r="J22" s="0"/>
-      <c r="K22" s="0"/>
-      <c r="L22" s="0"/>
-      <c r="M22" s="0"/>
-      <c r="N22" s="0"/>
-      <c r="O22" s="0"/>
-      <c r="P22" s="0"/>
-      <c r="Q22" s="0"/>
-      <c r="R22" s="0"/>
-      <c r="S22" s="0"/>
-      <c r="T22" s="0"/>
-      <c r="U22" s="0"/>
-      <c r="V22" s="0"/>
-      <c r="W22" s="0"/>
-      <c r="X22" s="0"/>
-      <c r="Y22" s="0"/>
-      <c r="Z22" s="0"/>
+      <c r="A22" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="0">
+        <v>0.013707364359083185</v>
+      </c>
+      <c r="D22" s="0">
+        <v>0.017453292519371413</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0.021199220679659639</v>
+      </c>
+      <c r="F22" s="0">
+        <v>-0.0012545726031601271</v>
+      </c>
+      <c r="G22" s="0">
+        <v>-0.0010087670169428348</v>
+      </c>
+      <c r="H22" s="0">
+        <v>-0.0007629614307255423</v>
+      </c>
+      <c r="I22" s="0">
+        <v>-0.00042574380420903901</v>
+      </c>
+      <c r="J22" s="0">
+        <v>-0.00018478611498954272</v>
+      </c>
+      <c r="K22" s="0">
+        <v>5.6171574229953533e-05</v>
+      </c>
+      <c r="L22" s="0">
+        <v>0.75990431919938872</v>
+      </c>
+      <c r="M22" s="0">
+        <v>0.76590653445397749</v>
+      </c>
+      <c r="N22" s="0">
+        <v>0.77190874970856627</v>
+      </c>
+      <c r="O22" s="0">
+        <v>-0.024077650341340285</v>
+      </c>
+      <c r="P22" s="0">
+        <v>-0.023343919346321077</v>
+      </c>
+      <c r="Q22" s="0">
+        <v>-0.022610188351301869</v>
+      </c>
+      <c r="R22" s="0">
+        <v>0.70571528874238576</v>
+      </c>
+      <c r="S22" s="0">
+        <v>0.71885447225468746</v>
+      </c>
+      <c r="T22" s="0">
+        <v>0.73199365576698916</v>
+      </c>
+      <c r="U22" s="0">
+        <v>0.0028037616377593164</v>
+      </c>
+      <c r="V22" s="0">
+        <v>0.0034020963077074696</v>
+      </c>
+      <c r="W22" s="0">
+        <v>0.0040004309776556233</v>
+      </c>
+      <c r="X22" s="0">
+        <v>-1.3328474363325851</v>
+      </c>
+      <c r="Y22" s="0">
+        <v>-1.3183224487353575</v>
+      </c>
+      <c r="Z22" s="0">
+        <v>-1.30379746113813</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>53</v>
+      </c>
       <c r="C23" s="0">
-        <v>0.016214084807763381</v>
+        <v>0.0014161869084656099</v>
       </c>
       <c r="D23" s="0">
-        <v>0.017453292519912116</v>
+        <v>0.0067443014418924483</v>
       </c>
       <c r="E23" s="0">
-        <v>0.018692500232060851</v>
+        <v>0.012072415975319287</v>
       </c>
       <c r="F23" s="0">
-        <v>-0.00091039367700386173</v>
+        <v>0.016107040367180015</v>
       </c>
       <c r="G23" s="0">
-        <v>-0.00082505806323233846</v>
+        <v>0.017453292517212615</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.0007397224494608152</v>
+        <v>0.018799544667245215</v>
       </c>
       <c r="I23" s="0">
-        <v>-0.0014887049301186446</v>
+        <v>0.0097398969087392762</v>
       </c>
       <c r="J23" s="0">
-        <v>-0.0014034586889579877</v>
+        <v>0.014843780063041991</v>
       </c>
       <c r="K23" s="0">
-        <v>-0.0013182124477973307</v>
+        <v>0.019947663217344706</v>
       </c>
       <c r="L23" s="0">
-        <v>0.79603727223596032</v>
+        <v>0.46061490593334115</v>
       </c>
       <c r="M23" s="0">
-        <v>0.79830887942947071</v>
+        <v>0.55041821181804151</v>
       </c>
       <c r="N23" s="0">
-        <v>0.80058048662298109</v>
+        <v>0.64022151770274183</v>
       </c>
       <c r="O23" s="0">
-        <v>-0.02231788906880448</v>
+        <v>0.023570207324685615</v>
       </c>
       <c r="P23" s="0">
-        <v>-0.022054230644288356</v>
+        <v>0.031681731141522188</v>
       </c>
       <c r="Q23" s="0">
-        <v>-0.021790572219772233</v>
+        <v>0.039793254958358761</v>
       </c>
       <c r="R23" s="0">
-        <v>0.78334977239418746</v>
+        <v>0.70892849109655542</v>
       </c>
       <c r="S23" s="0">
-        <v>0.7867695784144384</v>
+        <v>0.71930881827603943</v>
       </c>
       <c r="T23" s="0">
-        <v>0.79018938443468933</v>
+        <v>0.72968914545552344</v>
       </c>
       <c r="U23" s="0">
-        <v>0.0046357472113879895</v>
+        <v>-0.0013842959721612137</v>
       </c>
       <c r="V23" s="0">
-        <v>0.0048482401968164991</v>
+        <v>0.0012574120893398761</v>
       </c>
       <c r="W23" s="0">
-        <v>0.0050607331822450086</v>
+        <v>0.0038991201508409659</v>
       </c>
       <c r="X23" s="0">
-        <v>-4.8793139955749814</v>
+        <v>-14.12451902589267</v>
       </c>
       <c r="Y23" s="0">
-        <v>-4.8741376031672328</v>
+        <v>-12.813499964937403</v>
       </c>
       <c r="Z23" s="0">
-        <v>-4.8689612107594842</v>
+        <v>-11.502480903982136</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="0"/>
+        <v>1</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>54</v>
+      </c>
       <c r="C24" s="0">
-        <v>0.008143834074003346</v>
+        <v>-0.01050844804126874</v>
       </c>
       <c r="D24" s="0">
-        <v>0.012004931735748844</v>
+        <v>0.0022374601613092786</v>
       </c>
       <c r="E24" s="0">
-        <v>0.016006644040896644</v>
+        <v>0.014983368363887297</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0043185874538970879</v>
+        <v>0.014254528909639422</v>
       </c>
       <c r="G24" s="0">
-        <v>0.0052581474208596331</v>
+        <v>0.017453292299695673</v>
       </c>
       <c r="H24" s="0">
-        <v>0.0062030243778652752</v>
+        <v>0.020652055689751925</v>
       </c>
       <c r="I24" s="0">
-        <v>0.0025976889967945006</v>
+        <v>-0.024465310696951386</v>
       </c>
       <c r="J24" s="0">
-        <v>0.0051476727682184314</v>
+        <v>-0.01367303698536558</v>
       </c>
       <c r="K24" s="0">
-        <v>0.0078434278358210635</v>
+        <v>-0.0028807632737797746</v>
       </c>
       <c r="L24" s="0">
-        <v>0.63064330586018846</v>
+        <v>0.51354190851185855</v>
       </c>
       <c r="M24" s="0">
-        <v>0.67982723955681745</v>
+        <v>0.72663123454250578</v>
       </c>
       <c r="N24" s="0">
-        <v>0.73302452838011156</v>
+        <v>0.93972056057315301</v>
       </c>
       <c r="O24" s="0">
-        <v>-0.008762137713207668</v>
+        <v>0.0022492953001933373</v>
       </c>
       <c r="P24" s="0">
-        <v>-0.0040347066576059696</v>
+        <v>0.019512460884310322</v>
       </c>
       <c r="Q24" s="0">
-        <v>0.00078167233258981568</v>
+        <v>0.036775626468427303</v>
       </c>
       <c r="R24" s="0">
-        <v>0.67798340732751372</v>
+        <v>0.63265814190990344</v>
       </c>
       <c r="S24" s="0">
-        <v>0.68712580053432681</v>
+        <v>0.65098932280153687</v>
       </c>
       <c r="T24" s="0">
-        <v>0.69628575355925504</v>
+        <v>0.66932050369317031</v>
       </c>
       <c r="U24" s="0">
-        <v>0.0031155069436206878</v>
+        <v>-0.0049806858936737048</v>
       </c>
       <c r="V24" s="0">
-        <v>0.0048920774181784267</v>
+        <v>0.0022712253826531973</v>
       </c>
       <c r="W24" s="0">
-        <v>0.0068495526955889806</v>
+        <v>0.0095231366589800994</v>
       </c>
       <c r="X24" s="0">
-        <v>-5.3801846241341176</v>
+        <v>-8.1648067630080234</v>
       </c>
       <c r="Y24" s="0">
-        <v>-4.8702256502884378</v>
+        <v>-5.828822860391174</v>
       </c>
       <c r="Z24" s="0">
-        <v>-4.3446805315488106</v>
+        <v>-3.4928389577743251</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C25" s="0">
+        <v>0.015926698787334808</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0.017453292517401322</v>
+      </c>
+      <c r="E25" s="0">
+        <v>0.018979886247467836</v>
+      </c>
+      <c r="F25" s="0">
+        <v>0.0002372308497394618</v>
+      </c>
+      <c r="G25" s="0">
+        <v>0.00033901767099911282</v>
+      </c>
+      <c r="H25" s="0">
+        <v>0.00044080449225876385</v>
+      </c>
+      <c r="I25" s="0">
+        <v>-0.00070103014949686622</v>
+      </c>
+      <c r="J25" s="0">
+        <v>-0.00059935722425464287</v>
+      </c>
+      <c r="K25" s="0">
+        <v>-0.00049768429901241951</v>
+      </c>
+      <c r="L25" s="0">
+        <v>0.83310525303011318</v>
+      </c>
+      <c r="M25" s="0">
+        <v>0.83627083775466482</v>
+      </c>
+      <c r="N25" s="0">
+        <v>0.83943642247921646</v>
+      </c>
+      <c r="O25" s="0">
+        <v>-0.020980593382298393</v>
+      </c>
+      <c r="P25" s="0">
+        <v>-0.020634424317526833</v>
+      </c>
+      <c r="Q25" s="0">
+        <v>-0.020288255252755273</v>
+      </c>
+      <c r="R25" s="0">
+        <v>0.77318579145398403</v>
+      </c>
+      <c r="S25" s="0">
+        <v>0.7769962357136303</v>
+      </c>
+      <c r="T25" s="0">
+        <v>0.78080667997327657</v>
+      </c>
+      <c r="U25" s="0">
+        <v>0.0047762980301406192</v>
+      </c>
+      <c r="V25" s="0">
+        <v>0.005041269940573339</v>
+      </c>
+      <c r="W25" s="0">
+        <v>0.0053062418510060588</v>
+      </c>
+      <c r="X25" s="0">
+        <v>-1.5284534946008677</v>
+      </c>
+      <c r="Y25" s="0">
+        <v>-1.5222050675770109</v>
+      </c>
+      <c r="Z25" s="0">
+        <v>-1.5159566405531542</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="0">
+        <v>-0.0035980412807654094</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0.00091236484534524805</v>
+      </c>
+      <c r="E26" s="0">
+        <v>0.0054227709714559057</v>
+      </c>
+      <c r="F26" s="0">
+        <v>0.0040620650221549221</v>
+      </c>
+      <c r="G26" s="0">
+        <v>0.0052233535596161824</v>
+      </c>
+      <c r="H26" s="0">
+        <v>0.0063846420970774427</v>
+      </c>
+      <c r="I26" s="0">
+        <v>-0.0014179722335572651</v>
+      </c>
+      <c r="J26" s="0">
+        <v>0.0026708448057407718</v>
+      </c>
+      <c r="K26" s="0">
+        <v>0.0067596618450388082</v>
+      </c>
+      <c r="L26" s="0">
+        <v>0.70394191933709671</v>
+      </c>
+      <c r="M26" s="0">
+        <v>0.7985965272161929</v>
+      </c>
+      <c r="N26" s="0">
+        <v>0.89325113509528908</v>
+      </c>
+      <c r="O26" s="0">
+        <v>-0.018937464043055498</v>
+      </c>
+      <c r="P26" s="0">
+        <v>-0.011905387931345303</v>
+      </c>
+      <c r="Q26" s="0">
+        <v>-0.0048733118196351098</v>
+      </c>
+      <c r="R26" s="0">
+        <v>0.77957510796318341</v>
+      </c>
+      <c r="S26" s="0">
+        <v>0.78733178126878178</v>
+      </c>
+      <c r="T26" s="0">
+        <v>0.79508845457438016</v>
+      </c>
+      <c r="U26" s="0">
+        <v>0.0014744525664754956</v>
+      </c>
+      <c r="V26" s="0">
+        <v>0.0037440030307883125</v>
+      </c>
+      <c r="W26" s="0">
+        <v>0.0060135534951011298</v>
+      </c>
+      <c r="X26" s="0">
+        <v>4.9750912088604187</v>
+      </c>
+      <c r="Y26" s="0">
+        <v>6.1950307188115019</v>
+      </c>
+      <c r="Z26" s="0">
+        <v>7.4149702287625852</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="0">
+        <v>0.0072724644590942567</v>
+      </c>
+      <c r="D27" s="0">
+        <v>0.011196093733401538</v>
+      </c>
+      <c r="E27" s="0">
+        <v>0.01511972300770882</v>
+      </c>
+      <c r="F27" s="0">
+        <v>0.0021963045015732921</v>
+      </c>
+      <c r="G27" s="0">
+        <v>0.0034848484995604382</v>
+      </c>
+      <c r="H27" s="0">
+        <v>0.0047733924975475843</v>
+      </c>
+      <c r="I27" s="0">
+        <v>0.0058635863229251125</v>
+      </c>
+      <c r="J27" s="0">
+        <v>0.009293611641099481</v>
+      </c>
+      <c r="K27" s="0">
+        <v>0.01272363695927385</v>
+      </c>
+      <c r="L27" s="0">
+        <v>0.61283593338137332</v>
+      </c>
+      <c r="M27" s="0">
+        <v>0.6887147994692665</v>
+      </c>
+      <c r="N27" s="0">
+        <v>0.76459366555715969</v>
+      </c>
+      <c r="O27" s="0">
+        <v>-0.016922337042689778</v>
+      </c>
+      <c r="P27" s="0">
+        <v>-0.011095096785367553</v>
+      </c>
+      <c r="Q27" s="0">
+        <v>-0.0052678565280453293</v>
+      </c>
+      <c r="R27" s="0">
+        <v>0.78246104438553665</v>
+      </c>
+      <c r="S27" s="0">
+        <v>0.7886587586149707</v>
+      </c>
+      <c r="T27" s="0">
+        <v>0.79485647284440475</v>
+      </c>
+      <c r="U27" s="0">
+        <v>0.0088787818325945234</v>
+      </c>
+      <c r="V27" s="0">
+        <v>0.011710024866098671</v>
+      </c>
+      <c r="W27" s="0">
+        <v>0.014541267899602819</v>
+      </c>
+      <c r="X27" s="0">
+        <v>1.6392608180351558</v>
+      </c>
+      <c r="Y27" s="0">
+        <v>2.2878293888115224</v>
+      </c>
+      <c r="Z27" s="0">
+        <v>2.9363979595878891</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="0">
+        <v>0.0011283721962982124</v>
+      </c>
+      <c r="D28" s="0">
+        <v>0.0042286597021632243</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.0073289472080282358</v>
+      </c>
+      <c r="F28" s="0">
+        <v>-0.0040254493917219521</v>
+      </c>
+      <c r="G28" s="0">
+        <v>-0.0038511995436088355</v>
+      </c>
+      <c r="H28" s="0">
+        <v>-0.0036769496954957184</v>
+      </c>
+      <c r="I28" s="0">
+        <v>-0.00079033182746948672</v>
+      </c>
+      <c r="J28" s="0">
+        <v>-0.00061168844123753771</v>
+      </c>
+      <c r="K28" s="0">
+        <v>-0.00043304505500558869</v>
+      </c>
+      <c r="L28" s="0">
+        <v>0.69382194301938249</v>
+      </c>
+      <c r="M28" s="0">
+        <v>0.71568541391136242</v>
+      </c>
+      <c r="N28" s="0">
+        <v>0.73754888480334235</v>
+      </c>
+      <c r="O28" s="0">
+        <v>-0.026326403202325981</v>
+      </c>
+      <c r="P28" s="0">
+        <v>-0.024097099272062394</v>
+      </c>
+      <c r="Q28" s="0">
+        <v>-0.021867795341798807</v>
+      </c>
+      <c r="R28" s="0">
+        <v>0.77521936711806405</v>
+      </c>
+      <c r="S28" s="0">
+        <v>0.77996208892527064</v>
+      </c>
+      <c r="T28" s="0">
+        <v>0.78470481073247722</v>
+      </c>
+      <c r="U28" s="0">
+        <v>0.0072663045352364076</v>
+      </c>
+      <c r="V28" s="0">
+        <v>0.0077340234823370015</v>
+      </c>
+      <c r="W28" s="0">
+        <v>0.0082017424294375946</v>
+      </c>
+      <c r="X28" s="0">
+        <v>-1.2095881763647542</v>
+      </c>
+      <c r="Y28" s="0">
+        <v>-1.1971182925035482</v>
+      </c>
+      <c r="Z28" s="0">
+        <v>-1.1846484086423421</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="0">
+        <v>0.012578384304661832</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0.014513451509197514</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0.016448518713733196</v>
+      </c>
+      <c r="F29" s="0">
+        <v>0.00053839063354381466</v>
+      </c>
+      <c r="G29" s="0">
+        <v>0.00063636779315427152</v>
+      </c>
+      <c r="H29" s="0">
+        <v>0.00073434495276472839</v>
+      </c>
+      <c r="I29" s="0">
+        <v>0.00052586044307761134</v>
+      </c>
+      <c r="J29" s="0">
+        <v>0.00062246775653492664</v>
+      </c>
+      <c r="K29" s="0">
+        <v>0.00071907506999224194</v>
+      </c>
+      <c r="L29" s="0">
+        <v>0.73597542871481114</v>
+      </c>
+      <c r="M29" s="0">
+        <v>0.73904682137615274</v>
+      </c>
+      <c r="N29" s="0">
+        <v>0.74211821403749434</v>
+      </c>
+      <c r="O29" s="0">
+        <v>-0.016784699740555301</v>
+      </c>
+      <c r="P29" s="0">
+        <v>-0.016365294338818941</v>
+      </c>
+      <c r="Q29" s="0">
+        <v>-0.01594588893708258</v>
+      </c>
+      <c r="R29" s="0">
+        <v>0.7918925640017066</v>
+      </c>
+      <c r="S29" s="0">
+        <v>0.79713251792127915</v>
+      </c>
+      <c r="T29" s="0">
+        <v>0.8023724718408517</v>
+      </c>
+      <c r="U29" s="0">
+        <v>0.0063126202156576763</v>
+      </c>
+      <c r="V29" s="0">
+        <v>0.0066779867335785541</v>
+      </c>
+      <c r="W29" s="0">
+        <v>0.007043353251499432</v>
+      </c>
+      <c r="X29" s="0">
+        <v>-1.2056710101149437</v>
+      </c>
+      <c r="Y29" s="0">
+        <v>-1.2009307938634186</v>
+      </c>
+      <c r="Z29" s="0">
+        <v>-1.1961905776118935</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0" t="s">
+        <v>49</v>
+      </c>
+      <c r="B30" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="0">
+        <v>0.00029883780938541864</v>
+      </c>
+      <c r="D30" s="0">
+        <v>0.0055970298862912989</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0.010895221963197178</v>
+      </c>
+      <c r="F30" s="0">
+        <v>0.00083446279664967787</v>
+      </c>
+      <c r="G30" s="0">
+        <v>0.0032489448964018773</v>
+      </c>
+      <c r="H30" s="0">
+        <v>0.0056634269961540768</v>
+      </c>
+      <c r="I30" s="0">
+        <v>-0.042166396579258976</v>
+      </c>
+      <c r="J30" s="0">
+        <v>-0.03490658094773233</v>
+      </c>
+      <c r="K30" s="0">
+        <v>-0.027646765316205683</v>
+      </c>
+      <c r="L30" s="0">
+        <v>0.64102040757431511</v>
+      </c>
+      <c r="M30" s="0">
+        <v>0.70608603973600959</v>
+      </c>
+      <c r="N30" s="0">
+        <v>0.77115167189770406</v>
+      </c>
+      <c r="O30" s="0">
+        <v>-0.014163404665832949</v>
+      </c>
+      <c r="P30" s="0">
+        <v>-0.0069536287816648204</v>
+      </c>
+      <c r="Q30" s="0">
+        <v>0.00025614710250330703</v>
+      </c>
+      <c r="R30" s="0">
+        <v>0.76887358184804599</v>
+      </c>
+      <c r="S30" s="0">
+        <v>0.7768953528439484</v>
+      </c>
+      <c r="T30" s="0">
+        <v>0.78491712383985079</v>
+      </c>
+      <c r="U30" s="0">
+        <v>-0.0024279601051920749</v>
+      </c>
+      <c r="V30" s="0">
+        <v>0.002743102954592343</v>
+      </c>
+      <c r="W30" s="0">
+        <v>0.0079141660143767605</v>
+      </c>
+      <c r="X30" s="0">
+        <v>-0.21835378110881565</v>
+      </c>
+      <c r="Y30" s="0">
+        <v>1.0056479051994041</v>
+      </c>
+      <c r="Z30" s="0">
+        <v>2.2296495915076236</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="0">
+        <v>0.013720203543761149</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0.01745324358356435</v>
+      </c>
+      <c r="E31" s="0">
+        <v>0.021186283623367552</v>
+      </c>
+      <c r="F31" s="0">
+        <v>0.0044315523854698158</v>
+      </c>
+      <c r="G31" s="0">
+        <v>0.0046700322443743283</v>
+      </c>
+      <c r="H31" s="0">
+        <v>0.0049085121032788406</v>
+      </c>
+      <c r="I31" s="0">
+        <v>0.0014173791784749484</v>
+      </c>
+      <c r="J31" s="0">
+        <v>0.0016591033481765708</v>
+      </c>
+      <c r="K31" s="0">
+        <v>0.0019008275178781931</v>
+      </c>
+      <c r="L31" s="0">
+        <v>0.84206226100477444</v>
+      </c>
+      <c r="M31" s="0">
+        <v>0.8616279533935971</v>
+      </c>
+      <c r="N31" s="0">
+        <v>0.88119364578241977</v>
+      </c>
+      <c r="O31" s="0">
+        <v>-0.021939319099089617</v>
+      </c>
+      <c r="P31" s="0">
+        <v>-0.019834612050973123</v>
+      </c>
+      <c r="Q31" s="0">
+        <v>-0.017729905002856629</v>
+      </c>
+      <c r="R31" s="0">
+        <v>0.761675553725632</v>
+      </c>
+      <c r="S31" s="0">
+        <v>0.76766347334288254</v>
+      </c>
+      <c r="T31" s="0">
+        <v>0.77365139296013308</v>
+      </c>
+      <c r="U31" s="0">
+        <v>0.0046318776741087024</v>
+      </c>
+      <c r="V31" s="0">
+        <v>0.0053820111890289877</v>
+      </c>
+      <c r="W31" s="0">
+        <v>0.006132144703949273</v>
+      </c>
+      <c r="X31" s="0">
+        <v>-1.4003250910839293</v>
+      </c>
+      <c r="Y31" s="0">
+        <v>-1.3841130679223124</v>
+      </c>
+      <c r="Z31" s="0">
+        <v>-1.3679010447606954</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" s="0">
+        <v>-0.0015372399726809437</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0.002861981600862297</v>
+      </c>
+      <c r="E32" s="0">
+        <v>0.0072612031744055377</v>
+      </c>
+      <c r="F32" s="0">
+        <v>0.00202244187437403</v>
+      </c>
+      <c r="G32" s="0">
+        <v>0.0022263572925091922</v>
+      </c>
+      <c r="H32" s="0">
+        <v>0.0024302727106443544</v>
+      </c>
+      <c r="I32" s="0">
+        <v>0.0011203797736702827</v>
+      </c>
+      <c r="J32" s="0">
+        <v>0.001318533031136463</v>
+      </c>
+      <c r="K32" s="0">
+        <v>0.0015166862886026432</v>
+      </c>
+      <c r="L32" s="0">
+        <v>0.84399962389530137</v>
+      </c>
+      <c r="M32" s="0">
+        <v>0.85067472533421362</v>
+      </c>
+      <c r="N32" s="0">
+        <v>0.85734982677312588</v>
+      </c>
+      <c r="O32" s="0">
+        <v>-0.026378132522540739</v>
+      </c>
+      <c r="P32" s="0">
+        <v>-0.025442738508539984</v>
+      </c>
+      <c r="Q32" s="0">
+        <v>-0.024507344494539229</v>
+      </c>
+      <c r="R32" s="0">
+        <v>0.74965036445153477</v>
+      </c>
+      <c r="S32" s="0">
+        <v>0.76404861298612348</v>
+      </c>
+      <c r="T32" s="0">
+        <v>0.77844686152071219</v>
+      </c>
+      <c r="U32" s="0">
+        <v>0.00024506758769905139</v>
+      </c>
+      <c r="V32" s="0">
+        <v>0.0011122959199406969</v>
+      </c>
+      <c r="W32" s="0">
+        <v>0.0019795242521823426</v>
+      </c>
+      <c r="X32" s="0">
+        <v>-1.3794508376818664</v>
+      </c>
+      <c r="Y32" s="0">
+        <v>-1.3689218952364846</v>
+      </c>
+      <c r="Z32" s="0">
+        <v>-1.3583929527911027</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="0">
+        <v>0.0095228197203500505</v>
+      </c>
+      <c r="D33" s="0">
+        <v>0.017453292140364958</v>
+      </c>
+      <c r="E33" s="0">
+        <v>0.025383764560379864</v>
+      </c>
+      <c r="F33" s="0">
+        <v>0.0079201298398467266</v>
+      </c>
+      <c r="G33" s="0">
+        <v>0.009129012398896047</v>
+      </c>
+      <c r="H33" s="0">
+        <v>0.010337894957945367</v>
+      </c>
+      <c r="I33" s="0">
+        <v>-0.0019676368022261289</v>
+      </c>
+      <c r="J33" s="0">
+        <v>-0.00077310793215116375</v>
+      </c>
+      <c r="K33" s="0">
+        <v>0.00042142093792380128</v>
+      </c>
+      <c r="L33" s="0">
+        <v>0.7239044376678091</v>
+      </c>
+      <c r="M33" s="0">
+        <v>0.7369100869485562</v>
+      </c>
+      <c r="N33" s="0">
+        <v>0.7499157362293033</v>
+      </c>
+      <c r="O33" s="0">
+        <v>-0.00062768578129798183</v>
+      </c>
+      <c r="P33" s="0">
+        <v>0.0021440994592385816</v>
+      </c>
+      <c r="Q33" s="0">
+        <v>0.0049158846997751447</v>
+      </c>
+      <c r="R33" s="0">
+        <v>0.93005911797589747</v>
+      </c>
+      <c r="S33" s="0">
+        <v>0.96361767490984662</v>
+      </c>
+      <c r="T33" s="0">
+        <v>0.99717623184379578</v>
+      </c>
+      <c r="U33" s="0">
+        <v>0.0085410136931716695</v>
+      </c>
+      <c r="V33" s="0">
+        <v>0.011098701822122421</v>
+      </c>
+      <c r="W33" s="0">
+        <v>0.013656389951073173</v>
+      </c>
+      <c r="X33" s="0">
+        <v>-0.81046391138808727</v>
+      </c>
+      <c r="Y33" s="0">
+        <v>-0.77088292543353576</v>
+      </c>
+      <c r="Z33" s="0">
+        <v>-0.73130193947898425</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="0">
+        <v>0.0021569678281347102</v>
+      </c>
+      <c r="D34" s="0">
+        <v>0.0062349547125368256</v>
+      </c>
+      <c r="E34" s="0">
+        <v>0.010312941596938942</v>
+      </c>
+      <c r="F34" s="0">
+        <v>-0.019879313674572987</v>
+      </c>
+      <c r="G34" s="0">
+        <v>-0.01745329251924176</v>
+      </c>
+      <c r="H34" s="0">
+        <v>-0.015027271363910532</v>
+      </c>
+      <c r="I34" s="0">
+        <v>-0.0083453604583285448</v>
+      </c>
+      <c r="J34" s="0">
+        <v>-0.0016438410186502743</v>
+      </c>
+      <c r="K34" s="0">
+        <v>0.0050576784210279958</v>
+      </c>
+      <c r="L34" s="0">
+        <v>0.66973983872182707</v>
+      </c>
+      <c r="M34" s="0">
+        <v>0.7298955830058711</v>
+      </c>
+      <c r="N34" s="0">
+        <v>0.79005132728991512</v>
+      </c>
+      <c r="O34" s="0">
+        <v>-0.056358738397703549</v>
+      </c>
+      <c r="P34" s="0">
+        <v>-0.048981011378997047</v>
+      </c>
+      <c r="Q34" s="0">
+        <v>-0.041603284360290545</v>
+      </c>
+      <c r="R34" s="0">
+        <v>0.78982532379712678</v>
+      </c>
+      <c r="S34" s="0">
+        <v>0.79655530354900628</v>
+      </c>
+      <c r="T34" s="0">
+        <v>0.80328528330088578</v>
+      </c>
+      <c r="U34" s="0">
+        <v>0.0060860405463392022</v>
+      </c>
+      <c r="V34" s="0">
+        <v>0.010937073973987211</v>
+      </c>
+      <c r="W34" s="0">
+        <v>0.015788107401635221</v>
+      </c>
+      <c r="X34" s="0">
+        <v>1.3362644723759436</v>
+      </c>
+      <c r="Y34" s="0">
+        <v>2.3546364464618281</v>
+      </c>
+      <c r="Z34" s="0">
+        <v>3.3730084205477127</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0"/>
+      <c r="B35" s="0"/>
+      <c r="C35" s="0"/>
+      <c r="D35" s="0"/>
+      <c r="E35" s="0"/>
+      <c r="F35" s="0"/>
+      <c r="G35" s="0"/>
+      <c r="H35" s="0"/>
+      <c r="I35" s="0"/>
+      <c r="J35" s="0"/>
+      <c r="K35" s="0"/>
+      <c r="L35" s="0"/>
+      <c r="M35" s="0"/>
+      <c r="N35" s="0"/>
+      <c r="O35" s="0"/>
+      <c r="P35" s="0"/>
+      <c r="Q35" s="0"/>
+      <c r="R35" s="0"/>
+      <c r="S35" s="0"/>
+      <c r="T35" s="0"/>
+      <c r="U35" s="0"/>
+      <c r="V35" s="0"/>
+      <c r="W35" s="0"/>
+      <c r="X35" s="0"/>
+      <c r="Y35" s="0"/>
+      <c r="Z35" s="0"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="B36" s="0"/>
+      <c r="C36" s="0">
+        <v>0.0059239934424977683</v>
+      </c>
+      <c r="D36" s="0">
+        <v>0.010285833913631482</v>
+      </c>
+      <c r="E36" s="0">
+        <v>0.014679372580860139</v>
+      </c>
+      <c r="F36" s="0">
+        <v>0.0018522039552924475</v>
+      </c>
+      <c r="G36" s="0">
+        <v>0.0028172041288352526</v>
+      </c>
+      <c r="H36" s="0">
+        <v>0.0037859042008466315</v>
+      </c>
+      <c r="I36" s="0">
+        <v>-0.0038058414411645055</v>
+      </c>
+      <c r="J36" s="0">
+        <v>-0.0012034856988180937</v>
+      </c>
+      <c r="K36" s="0">
+        <v>0.001426462812858827</v>
+      </c>
+      <c r="L36" s="0">
+        <v>0.68330178267752662</v>
+      </c>
+      <c r="M36" s="0">
+        <v>0.72742612026584041</v>
+      </c>
+      <c r="N36" s="0">
+        <v>0.7726778708313764</v>
+      </c>
+      <c r="O36" s="0">
+        <v>-0.016500347493107158</v>
+      </c>
+      <c r="P36" s="0">
+        <v>-0.012212461434048237</v>
+      </c>
+      <c r="Q36" s="0">
+        <v>-0.0078999326301217518</v>
+      </c>
+      <c r="R36" s="0">
+        <v>0.74398660098166547</v>
+      </c>
+      <c r="S36" s="0">
+        <v>0.75422059128121855</v>
+      </c>
+      <c r="T36" s="0">
+        <v>0.7644778391219188</v>
+      </c>
+      <c r="U36" s="0">
+        <v>0.0033194601865746023</v>
+      </c>
+      <c r="V36" s="0">
+        <v>0.0054053183331745731</v>
+      </c>
+      <c r="W36" s="0">
+        <v>0.0075299877367353049</v>
+      </c>
+      <c r="X36" s="0">
+        <v>-1.4895051069956939</v>
+      </c>
+      <c r="Y36" s="0">
+        <v>-0.97063123992629352</v>
+      </c>
+      <c r="Z36" s="0">
+        <v>-0.4478602563623364</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37" s="0"/>
+      <c r="C37" s="0">
+        <v>0.0078027056630883274</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0.0063436560910575066</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0.005970309495343204</v>
+      </c>
+      <c r="F37" s="0">
+        <v>0.0080963862728409084</v>
+      </c>
+      <c r="G37" s="0">
+        <v>0.0082512267126548054</v>
+      </c>
+      <c r="H37" s="0">
+        <v>0.0085203695121961725</v>
+      </c>
+      <c r="I37" s="0">
+        <v>0.012808154968450279</v>
+      </c>
+      <c r="J37" s="0">
+        <v>0.010885495966840656</v>
+      </c>
+      <c r="K37" s="0">
+        <v>0.0098096612580066255</v>
+      </c>
+      <c r="L37" s="0">
+        <v>0.15094472247564628</v>
+      </c>
+      <c r="M37" s="0">
+        <v>0.14107817829196517</v>
+      </c>
+      <c r="N37" s="0">
+        <v>0.14791136378414768</v>
+      </c>
+      <c r="O37" s="0">
+        <v>0.01799916052200155</v>
+      </c>
+      <c r="P37" s="0">
+        <v>0.019844354150601776</v>
+      </c>
+      <c r="Q37" s="0">
+        <v>0.022477410833440122</v>
+      </c>
+      <c r="R37" s="0">
+        <v>0.13966287454357337</v>
+      </c>
+      <c r="S37" s="0">
+        <v>0.14207696560729199</v>
+      </c>
+      <c r="T37" s="0">
+        <v>0.1447216160998156</v>
+      </c>
+      <c r="U37" s="0">
+        <v>0.0039363205079549126</v>
+      </c>
+      <c r="V37" s="0">
+        <v>0.0034039719515877843</v>
+      </c>
+      <c r="W37" s="0">
+        <v>0.0040394108361086929</v>
+      </c>
+      <c r="X37" s="0">
+        <v>4.3708362768581059</v>
+      </c>
+      <c r="Y37" s="0">
+        <v>4.1500224482495032</v>
+      </c>
+      <c r="Z37" s="0">
+        <v>4.0487032119693058</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0"/>
+      <c r="B38" s="0"/>
+      <c r="C38" s="0"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
+      <c r="G38" s="0"/>
+      <c r="H38" s="0"/>
+      <c r="I38" s="0"/>
+      <c r="J38" s="0"/>
+      <c r="K38" s="0"/>
+      <c r="L38" s="0"/>
+      <c r="M38" s="0"/>
+      <c r="N38" s="0"/>
+      <c r="O38" s="0"/>
+      <c r="P38" s="0"/>
+      <c r="Q38" s="0"/>
+      <c r="R38" s="0"/>
+      <c r="S38" s="0"/>
+      <c r="T38" s="0"/>
+      <c r="U38" s="0"/>
+      <c r="V38" s="0"/>
+      <c r="W38" s="0"/>
+      <c r="X38" s="0"/>
+      <c r="Y38" s="0"/>
+      <c r="Z38" s="0"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="0"/>
+      <c r="C39" s="0">
+        <v>0.016654541493856381</v>
+      </c>
+      <c r="D39" s="0">
+        <v>0.017453292512686586</v>
+      </c>
+      <c r="E39" s="0">
+        <v>0.018252043531516791</v>
+      </c>
+      <c r="F39" s="0">
+        <v>-0.00059067856365031541</v>
+      </c>
+      <c r="G39" s="0">
+        <v>-0.00053290498607456343</v>
+      </c>
+      <c r="H39" s="0">
+        <v>-0.00047513140849881144</v>
+      </c>
+      <c r="I39" s="0">
+        <v>-0.00058629083535828802</v>
+      </c>
+      <c r="J39" s="0">
+        <v>-0.00052842152268392875</v>
+      </c>
+      <c r="K39" s="0">
+        <v>-0.00047055221000956947</v>
+      </c>
+      <c r="L39" s="0">
+        <v>0.76869947234730085</v>
+      </c>
+      <c r="M39" s="0">
+        <v>0.77018705242982866</v>
+      </c>
+      <c r="N39" s="0">
+        <v>0.77167463251235646</v>
+      </c>
+      <c r="O39" s="0">
+        <v>-0.020851638596024669</v>
+      </c>
+      <c r="P39" s="0">
+        <v>-0.020666049260914258</v>
+      </c>
+      <c r="Q39" s="0">
+        <v>-0.020480459925803846</v>
+      </c>
+      <c r="R39" s="0">
+        <v>0.76868072374979624</v>
+      </c>
+      <c r="S39" s="0">
+        <v>0.77059932171555834</v>
+      </c>
+      <c r="T39" s="0">
+        <v>0.77251791968132044</v>
+      </c>
+      <c r="U39" s="0">
+        <v>0.0048057031500960568</v>
+      </c>
+      <c r="V39" s="0">
+        <v>0.0049546038114255527</v>
+      </c>
+      <c r="W39" s="0">
+        <v>0.0051035044727550487</v>
+      </c>
+      <c r="X39" s="0">
+        <v>-1.3318646748960894</v>
+      </c>
+      <c r="Y39" s="0">
+        <v>-1.328377519806448</v>
+      </c>
+      <c r="Z39" s="0">
+        <v>-1.3248903647168067</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="0"/>
+      <c r="C40" s="0">
+        <v>0.0062948540387315673</v>
+      </c>
+      <c r="D40" s="0">
+        <v>0.01038069511293975</v>
+      </c>
+      <c r="E40" s="0">
+        <v>0.014528302223952483</v>
+      </c>
+      <c r="F40" s="0">
+        <v>0.0019640068905455561</v>
+      </c>
+      <c r="G40" s="0">
+        <v>0.0028784957014502447</v>
+      </c>
+      <c r="H40" s="0">
+        <v>0.003799828603846752</v>
+      </c>
+      <c r="I40" s="0">
+        <v>-0.0032225018230638875</v>
+      </c>
+      <c r="J40" s="0">
+        <v>-0.00082807258582418431</v>
+      </c>
+      <c r="K40" s="0">
+        <v>0.0016172329135141035</v>
+      </c>
+      <c r="L40" s="0">
+        <v>0.67015591883834702</v>
+      </c>
+      <c r="M40" s="0">
+        <v>0.71143826703613788</v>
+      </c>
+      <c r="N40" s="0">
+        <v>0.75427287832060441</v>
+      </c>
+      <c r="O40" s="0">
+        <v>-0.015613635230983887</v>
+      </c>
+      <c r="P40" s="0">
+        <v>-0.011518248852936943</v>
+      </c>
+      <c r="Q40" s="0">
+        <v>-0.0073764968604782284</v>
+      </c>
+      <c r="R40" s="0">
+        <v>0.72693867146196078</v>
+      </c>
+      <c r="S40" s="0">
+        <v>0.73669809436240719</v>
+      </c>
+      <c r="T40" s="0">
+        <v>0.7464861878730158</v>
+      </c>
+      <c r="U40" s="0">
+        <v>0.0033813161655423009</v>
+      </c>
+      <c r="V40" s="0">
+        <v>0.0053331988948411664</v>
+      </c>
+      <c r="W40" s="0">
+        <v>0.0073559565554233378</v>
+      </c>
+      <c r="X40" s="0">
+        <v>-1.3125056418205938</v>
+      </c>
+      <c r="Y40" s="0">
+        <v>-0.83054572791759818</v>
+      </c>
+      <c r="Z40" s="0">
+        <v>-0.341403392833596</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="0"/>
-      <c r="C25" s="0">
-        <v>0.0080387383752966168</v>
-      </c>
-      <c r="D25" s="0">
-        <v>0.0056296230373619723</v>
-      </c>
-      <c r="E25" s="0">
-        <v>0.0051857378740641988</v>
-      </c>
-      <c r="F25" s="0">
-        <v>0.0065556155542873555</v>
-      </c>
-      <c r="G25" s="0">
-        <v>0.007302299525629336</v>
-      </c>
-      <c r="H25" s="0">
-        <v>0.0080905878848438473</v>
-      </c>
-      <c r="I25" s="0">
-        <v>0.010741686063367201</v>
-      </c>
-      <c r="J25" s="0">
-        <v>0.010338553512841676</v>
-      </c>
-      <c r="K25" s="0">
-        <v>0.011152906237080399</v>
-      </c>
-      <c r="L25" s="0">
-        <v>0.20815021018180946</v>
-      </c>
-      <c r="M25" s="0">
-        <v>0.21202288225224489</v>
-      </c>
-      <c r="N25" s="0">
-        <v>0.22762113562504643</v>
-      </c>
-      <c r="O25" s="0">
-        <v>0.018896957168889825</v>
-      </c>
-      <c r="P25" s="0">
-        <v>0.021925969176324844</v>
-      </c>
-      <c r="Q25" s="0">
-        <v>0.025764644687891105</v>
-      </c>
-      <c r="R25" s="0">
-        <v>0.20903759797876584</v>
-      </c>
-      <c r="S25" s="0">
-        <v>0.21185015327583245</v>
-      </c>
-      <c r="T25" s="0">
-        <v>0.21473139240854183</v>
-      </c>
-      <c r="U25" s="0">
-        <v>0.0033204341162849003</v>
-      </c>
-      <c r="V25" s="0">
-        <v>0.00277786316886274</v>
-      </c>
-      <c r="W25" s="0">
-        <v>0.0036486791494186291</v>
-      </c>
-      <c r="X25" s="0">
-        <v>5.6092261744153378</v>
-      </c>
-      <c r="Y25" s="0">
-        <v>4.9859464336081976</v>
-      </c>
-      <c r="Z25" s="0">
-        <v>4.4796224141461032</v>
+      <c r="B41" s="0"/>
+      <c r="C41" s="0">
+        <v>0.0076682430788748753</v>
+      </c>
+      <c r="D41" s="0">
+        <v>0.006213051884638012</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0.0059216440823671168</v>
+      </c>
+      <c r="F41" s="0">
+        <v>0.0078065175018334999</v>
+      </c>
+      <c r="G41" s="0">
+        <v>0.0079450887709791879</v>
+      </c>
+      <c r="H41" s="0">
+        <v>0.0081991608823308772</v>
+      </c>
+      <c r="I41" s="0">
+        <v>0.012548434285931923</v>
+      </c>
+      <c r="J41" s="0">
+        <v>0.010583904407155799</v>
+      </c>
+      <c r="K41" s="0">
+        <v>0.0094700851684251606</v>
+      </c>
+      <c r="L41" s="0">
+        <v>0.17130076466939656</v>
+      </c>
+      <c r="M41" s="0">
+        <v>0.16823803381748387</v>
+      </c>
+      <c r="N41" s="0">
+        <v>0.17711065308827972</v>
+      </c>
+      <c r="O41" s="0">
+        <v>0.018175499975477367</v>
+      </c>
+      <c r="P41" s="0">
+        <v>0.019768867983520691</v>
+      </c>
+      <c r="Q41" s="0">
+        <v>0.022176124962773564</v>
+      </c>
+      <c r="R41" s="0">
+        <v>0.16887390285650622</v>
+      </c>
+      <c r="S41" s="0">
+        <v>0.17145762948708951</v>
+      </c>
+      <c r="T41" s="0">
+        <v>0.17420703638572255</v>
+      </c>
+      <c r="U41" s="0">
+        <v>0.0037630496962008262</v>
+      </c>
+      <c r="V41" s="0">
+        <v>0.0032643271202314334</v>
+      </c>
+      <c r="W41" s="0">
+        <v>0.0039178975199886407</v>
+      </c>
+      <c r="X41" s="0">
+        <v>4.2867999113955504</v>
+      </c>
+      <c r="Y41" s="0">
+        <v>4.0540382108696118</v>
+      </c>
+      <c r="Z41" s="0">
+        <v>3.9403232894017921</v>
       </c>
     </row>
   </sheetData>

--- a/processing26/resultsTable_BOOM.xlsx
+++ b/processing26/resultsTable_BOOM.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="783" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="848" uniqueCount="60">
   <si>
     <t>fname</t>
   </si>
@@ -188,6 +188,12 @@
   </si>
   <si>
     <t>463</t>
+  </si>
+  <si>
+    <t>552</t>
+  </si>
+  <si>
+    <t>389</t>
   </si>
 </sst>
 </file>
@@ -238,11 +244,11 @@
   <cols>
     <col min="1" max="1" width="19.7109375" customWidth="true"/>
     <col min="2" max="2" width="8.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.42578125" customWidth="true"/>
+    <col min="3" max="3" width="15.42578125" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
     <col min="5" max="5" width="14.7109375" customWidth="true"/>
     <col min="6" max="6" width="15.7109375" customWidth="true"/>
-    <col min="7" max="7" width="16.42578125" customWidth="true"/>
+    <col min="7" max="7" width="15.7109375" customWidth="true"/>
     <col min="8" max="8" width="16.42578125" customWidth="true"/>
     <col min="9" max="9" width="16.42578125" customWidth="true"/>
     <col min="10" max="10" width="16.42578125" customWidth="true"/>
@@ -257,11 +263,11 @@
     <col min="19" max="19" width="12.7109375" customWidth="true"/>
     <col min="20" max="20" width="12.7109375" customWidth="true"/>
     <col min="21" max="21" width="15.7109375" customWidth="true"/>
-    <col min="22" max="22" width="16.42578125" customWidth="true"/>
+    <col min="22" max="22" width="15.7109375" customWidth="true"/>
     <col min="23" max="23" width="14.7109375" customWidth="true"/>
-    <col min="24" max="24" width="13.42578125" customWidth="true"/>
-    <col min="25" max="25" width="12.7109375" customWidth="true"/>
-    <col min="26" max="26" width="12.42578125" customWidth="true"/>
+    <col min="24" max="24" width="12.42578125" customWidth="true"/>
+    <col min="25" max="25" width="13.42578125" customWidth="true"/>
+    <col min="26" max="26" width="12.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -352,76 +358,76 @@
         <v>53</v>
       </c>
       <c r="C2" s="0">
-        <v>0.01396331252214063</v>
+        <v>0.013789364735477656</v>
       </c>
       <c r="D2" s="0">
-        <v>0.017453292503120378</v>
+        <v>0.017453292503013026</v>
       </c>
       <c r="E2" s="0">
-        <v>0.020943272484100127</v>
+        <v>0.021117220270548395</v>
       </c>
       <c r="F2" s="0">
-        <v>-0.0037429023617660843</v>
+        <v>-0.0037649500766066186</v>
       </c>
       <c r="G2" s="0">
-        <v>-0.0035047917795720685</v>
+        <v>-0.0035157987521762905</v>
       </c>
       <c r="H2" s="0">
-        <v>-0.0032666811973780527</v>
+        <v>-0.0032666474277459625</v>
       </c>
       <c r="I2" s="0">
-        <v>-0.0021611005139847038</v>
+        <v>-0.0022357718270684221</v>
       </c>
       <c r="J2" s="0">
-        <v>-0.0019255026022217011</v>
+        <v>-0.0019892373487772445</v>
       </c>
       <c r="K2" s="0">
-        <v>-0.0016899046904586983</v>
+        <v>-0.0017427028704860667</v>
       </c>
       <c r="L2" s="0">
-        <v>0.76613527916717017</v>
+        <v>0.76592197776701265</v>
       </c>
       <c r="M2" s="0">
-        <v>0.77182873020347931</v>
+        <v>0.77190200431073486</v>
       </c>
       <c r="N2" s="0">
-        <v>0.77752218123978845</v>
+        <v>0.77788203085445706</v>
       </c>
       <c r="O2" s="0">
-        <v>-0.028378463408601545</v>
+        <v>-0.028437436168087527</v>
       </c>
       <c r="P2" s="0">
-        <v>-0.027663214444327868</v>
+        <v>-0.027687880428588298</v>
       </c>
       <c r="Q2" s="0">
-        <v>-0.026947965480054192</v>
+        <v>-0.02693832468908907</v>
       </c>
       <c r="R2" s="0">
-        <v>0.78598875336646601</v>
+        <v>0.78348652238770444</v>
       </c>
       <c r="S2" s="0">
-        <v>0.7993167571510249</v>
+        <v>0.79742890382097742</v>
       </c>
       <c r="T2" s="0">
-        <v>0.8126447609355838</v>
+        <v>0.8113712852542504</v>
       </c>
       <c r="U2" s="0">
-        <v>0.0028068574349667244</v>
+        <v>0.0027042085769106495</v>
       </c>
       <c r="V2" s="0">
-        <v>0.0033773159816749801</v>
+        <v>0.0033013750331028595</v>
       </c>
       <c r="W2" s="0">
-        <v>0.0039477745283832359</v>
+        <v>0.0038985414892950695</v>
       </c>
       <c r="X2" s="0">
-        <v>-2.6907441168536628</v>
+        <v>-3.0794455407677832</v>
       </c>
       <c r="Y2" s="0">
-        <v>-2.6770212812168168</v>
+        <v>-3.0650868696812887</v>
       </c>
       <c r="Z2" s="0">
-        <v>-2.6632984455799709</v>
+        <v>-3.0507281985947943</v>
       </c>
     </row>
     <row r="3">
@@ -432,76 +438,76 @@
         <v>54</v>
       </c>
       <c r="C3" s="0">
-        <v>0.013408984729205188</v>
+        <v>0.013272923465039577</v>
       </c>
       <c r="D3" s="0">
-        <v>0.01745329250841993</v>
+        <v>0.017453292508389749</v>
       </c>
       <c r="E3" s="0">
-        <v>0.021497600287634672</v>
+        <v>0.021633661551739923</v>
       </c>
       <c r="F3" s="0">
-        <v>-0.001328611274311566</v>
+        <v>-0.0013446155751278485</v>
       </c>
       <c r="G3" s="0">
-        <v>-0.0010648982225634181</v>
+        <v>-0.0010725028552350162</v>
       </c>
       <c r="H3" s="0">
-        <v>-0.00080118517081527018</v>
+        <v>-0.00080039013534218386</v>
       </c>
       <c r="I3" s="0">
-        <v>-0.00056643823575723345</v>
+        <v>-0.0006157335270882405</v>
       </c>
       <c r="J3" s="0">
-        <v>-0.00030782478566889821</v>
+        <v>-0.0003488724104882582</v>
       </c>
       <c r="K3" s="0">
-        <v>-4.9211335580563026e-05</v>
+        <v>-8.2011293888275909e-05</v>
       </c>
       <c r="L3" s="0">
-        <v>0.76176689061789737</v>
+        <v>0.76231143840098814</v>
       </c>
       <c r="M3" s="0">
-        <v>0.76826325077553759</v>
+        <v>0.76903203038112622</v>
       </c>
       <c r="N3" s="0">
-        <v>0.7747596109331778</v>
+        <v>0.7757526223612643</v>
       </c>
       <c r="O3" s="0">
-        <v>-0.024440856561955271</v>
+        <v>-0.024548590833529397</v>
       </c>
       <c r="P3" s="0">
-        <v>-0.023650984069770772</v>
+        <v>-0.023732741175155326</v>
       </c>
       <c r="Q3" s="0">
-        <v>-0.022861111577586274</v>
+        <v>-0.022916891516781255</v>
       </c>
       <c r="R3" s="0">
-        <v>0.69807602993309303</v>
+        <v>0.69508160073771541</v>
       </c>
       <c r="S3" s="0">
-        <v>0.71220180743586403</v>
+        <v>0.70965555866349594</v>
       </c>
       <c r="T3" s="0">
-        <v>0.72632758493863503</v>
+        <v>0.72422951658927648</v>
       </c>
       <c r="U3" s="0">
-        <v>0.0027174470726938236</v>
+        <v>0.0026799353094266454</v>
       </c>
       <c r="V3" s="0">
-        <v>0.0033600419737656365</v>
+        <v>0.0033431675579997668</v>
       </c>
       <c r="W3" s="0">
-        <v>0.0040026368748374494</v>
+        <v>0.0040063998065728882</v>
       </c>
       <c r="X3" s="0">
-        <v>-2.6135340710386386</v>
+        <v>-2.9474697155821588</v>
       </c>
       <c r="Y3" s="0">
-        <v>-2.5979751959260282</v>
+        <v>-2.9314154207200205</v>
       </c>
       <c r="Z3" s="0">
-        <v>-2.5824163208134179</v>
+        <v>-2.9153611258578822</v>
       </c>
     </row>
     <row r="4">
@@ -512,76 +518,76 @@
         <v>53</v>
       </c>
       <c r="C4" s="0">
-        <v>-0.0013417584826978177</v>
+        <v>-0.0014961367590251174</v>
       </c>
       <c r="D4" s="0">
-        <v>0.004654915519363958</v>
+        <v>0.0043617882135721393</v>
       </c>
       <c r="E4" s="0">
-        <v>0.010651589521425734</v>
+        <v>0.010219713186169396</v>
       </c>
       <c r="F4" s="0">
-        <v>0.015963086038584862</v>
+        <v>0.016006950055562321</v>
       </c>
       <c r="G4" s="0">
-        <v>0.017453292494177649</v>
+        <v>0.017453292482905839</v>
       </c>
       <c r="H4" s="0">
-        <v>0.018943498949770435</v>
+        <v>0.018899634910249357</v>
       </c>
       <c r="I4" s="0">
-        <v>0.0094467991643588673</v>
+        <v>0.0051579618589314598</v>
       </c>
       <c r="J4" s="0">
-        <v>0.015167746205747523</v>
+        <v>0.010659936300430507</v>
       </c>
       <c r="K4" s="0">
-        <v>0.020888693247136179</v>
+        <v>0.016161910741929554</v>
       </c>
       <c r="L4" s="0">
-        <v>0.47109497824202029</v>
+        <v>0.47379878035489675</v>
       </c>
       <c r="M4" s="0">
-        <v>0.57059592841325846</v>
+        <v>0.5705292046185334</v>
       </c>
       <c r="N4" s="0">
-        <v>0.67009687858449663</v>
+        <v>0.66725962888217005</v>
       </c>
       <c r="O4" s="0">
-        <v>0.021031894077326391</v>
+        <v>0.021292355699833565</v>
       </c>
       <c r="P4" s="0">
-        <v>0.03001803670608497</v>
+        <v>0.030029005992636068</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.039004179334843549</v>
+        <v>0.038765656285438571</v>
       </c>
       <c r="R4" s="0">
-        <v>0.71663838522350953</v>
+        <v>0.71361677076428109</v>
       </c>
       <c r="S4" s="0">
-        <v>0.72801256309460505</v>
+        <v>0.72467096508954521</v>
       </c>
       <c r="T4" s="0">
-        <v>0.73938674096570056</v>
+        <v>0.73572515941480932</v>
       </c>
       <c r="U4" s="0">
-        <v>-0.0025233906445823345</v>
+        <v>-0.0027780797252905543</v>
       </c>
       <c r="V4" s="0">
-        <v>0.0004498420919653482</v>
+        <v>0.00011365456806166264</v>
       </c>
       <c r="W4" s="0">
-        <v>0.0034230748285130311</v>
+        <v>0.0030053888614138798</v>
       </c>
       <c r="X4" s="0">
-        <v>-15.757547883951229</v>
+        <v>-16.517945613740686</v>
       </c>
       <c r="Y4" s="0">
-        <v>-14.39022257472992</v>
+        <v>-15.218991800973937</v>
       </c>
       <c r="Z4" s="0">
-        <v>-13.022897265508611</v>
+        <v>-13.92003798820719</v>
       </c>
     </row>
     <row r="5">
@@ -592,76 +598,76 @@
         <v>54</v>
       </c>
       <c r="C5" s="0">
-        <v>-0.018950828486952672</v>
+        <v>-0.020295010777966173</v>
       </c>
       <c r="D5" s="0">
-        <v>-0.0045505985132094492</v>
+        <v>-0.0059297543062454315</v>
       </c>
       <c r="E5" s="0">
-        <v>0.0098496314605337754</v>
+        <v>0.0084355021654753115</v>
       </c>
       <c r="F5" s="0">
-        <v>0.013328792823931956</v>
+        <v>0.014009947408095276</v>
       </c>
       <c r="G5" s="0">
-        <v>0.016846311892046311</v>
+        <v>0.017453285544585629</v>
       </c>
       <c r="H5" s="0">
-        <v>0.020363830960160666</v>
+        <v>0.020896623681075983</v>
       </c>
       <c r="I5" s="0">
-        <v>0.00091588324055721059</v>
+        <v>-0.014913387390745228</v>
       </c>
       <c r="J5" s="0">
-        <v>0.012342268425372629</v>
+        <v>-0.0038742611520644543</v>
       </c>
       <c r="K5" s="0">
-        <v>0.023768653610188047</v>
+        <v>0.0071648650866163186</v>
       </c>
       <c r="L5" s="0">
-        <v>0.46016724161439859</v>
+        <v>0.40857647063153557</v>
       </c>
       <c r="M5" s="0">
-        <v>0.66731472877182663</v>
+        <v>0.60973058860080409</v>
       </c>
       <c r="N5" s="0">
-        <v>0.87446221592925466</v>
+        <v>0.81088470657007261</v>
       </c>
       <c r="O5" s="0">
-        <v>0.0054714685944366043</v>
+        <v>0.011294394925583838</v>
       </c>
       <c r="P5" s="0">
-        <v>0.022567676588541259</v>
+        <v>0.027976818135072499</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.039663884582645914</v>
+        <v>0.04465924134456116</v>
       </c>
       <c r="R5" s="0">
-        <v>0.65537634227538211</v>
+        <v>0.64095914820381605</v>
       </c>
       <c r="S5" s="0">
-        <v>0.67597206178448432</v>
+        <v>0.66133889983724714</v>
       </c>
       <c r="T5" s="0">
-        <v>0.69656778129358654</v>
+        <v>0.68171865147067823</v>
       </c>
       <c r="U5" s="0">
-        <v>-0.008674727852426737</v>
+        <v>-0.01096191839446556</v>
       </c>
       <c r="V5" s="0">
-        <v>-0.0004679297761653552</v>
+        <v>-0.002857660904323182</v>
       </c>
       <c r="W5" s="0">
-        <v>0.0077388683000960273</v>
+        <v>0.0052465965858191962</v>
       </c>
       <c r="X5" s="0">
-        <v>-9.2543100205261197</v>
+        <v>-15.216326855102698</v>
       </c>
       <c r="Y5" s="0">
-        <v>-6.921601628638685</v>
+        <v>-13.208647899470209</v>
       </c>
       <c r="Z5" s="0">
-        <v>-4.5888932367512494</v>
+        <v>-11.20096894383772</v>
       </c>
     </row>
     <row r="6">
@@ -672,76 +678,76 @@
         <v>53</v>
       </c>
       <c r="C6" s="0">
-        <v>0.015599810570246618</v>
+        <v>0.015361750531484607</v>
       </c>
       <c r="D6" s="0">
-        <v>0.017453292519912116</v>
+        <v>0.017453292519912345</v>
       </c>
       <c r="E6" s="0">
-        <v>0.019306774469577612</v>
+        <v>0.019544834508340082</v>
       </c>
       <c r="F6" s="0">
-        <v>0.00015613885690105982</v>
+        <v>0.0001129276946706942</v>
       </c>
       <c r="G6" s="0">
-        <v>0.00027925942525269332</v>
+        <v>0.00025160247784230118</v>
       </c>
       <c r="H6" s="0">
-        <v>0.00040237999360432682</v>
+        <v>0.00039027726101390815</v>
       </c>
       <c r="I6" s="0">
-        <v>-0.00075007412989358882</v>
+        <v>-0.00080475592410434165</v>
       </c>
       <c r="J6" s="0">
-        <v>-0.00062708389928831576</v>
+        <v>-0.00066622692806290421</v>
       </c>
       <c r="K6" s="0">
-        <v>-0.00050409366868304269</v>
+        <v>-0.00052769793202146677</v>
       </c>
       <c r="L6" s="0">
-        <v>0.83293543109890222</v>
+        <v>0.83255988639118184</v>
       </c>
       <c r="M6" s="0">
-        <v>0.83678858142891255</v>
+        <v>0.83691316344508615</v>
       </c>
       <c r="N6" s="0">
-        <v>0.84064173175892287</v>
+        <v>0.84126644049899046</v>
       </c>
       <c r="O6" s="0">
-        <v>-0.021227855633374499</v>
+        <v>-0.021347135891928722</v>
       </c>
       <c r="P6" s="0">
-        <v>-0.020807657361311991</v>
+        <v>-0.020873109098434428</v>
       </c>
       <c r="Q6" s="0">
-        <v>-0.020387459089249483</v>
+        <v>-0.020399082304940135</v>
       </c>
       <c r="R6" s="0">
-        <v>0.77252425463975261</v>
+        <v>0.7714469896561964</v>
       </c>
       <c r="S6" s="0">
-        <v>0.77713902391861678</v>
+        <v>0.77664369288897761</v>
       </c>
       <c r="T6" s="0">
-        <v>0.78175379319748095</v>
+        <v>0.78184039612175882</v>
       </c>
       <c r="U6" s="0">
-        <v>0.0046007636542071398</v>
+        <v>0.0045163410581593689</v>
       </c>
       <c r="V6" s="0">
-        <v>0.004921389983799318</v>
+        <v>0.0048774597831532807</v>
       </c>
       <c r="W6" s="0">
-        <v>0.0052420163133914963</v>
+        <v>0.0052385785081471925</v>
       </c>
       <c r="X6" s="0">
-        <v>-2.653427405763749</v>
+        <v>-2.8011517790437703</v>
       </c>
       <c r="Y6" s="0">
-        <v>-2.6458844311730778</v>
+        <v>-2.7926569173905911</v>
       </c>
       <c r="Z6" s="0">
-        <v>-2.6383414565824066</v>
+        <v>-2.7841620557374118</v>
       </c>
     </row>
     <row r="7">
@@ -752,76 +758,76 @@
         <v>53</v>
       </c>
       <c r="C7" s="0">
-        <v>-0.003530604971813095</v>
+        <v>-0.0034982076166996954</v>
       </c>
       <c r="D7" s="0">
-        <v>0.0010278052112566805</v>
+        <v>0.0009934669262226855</v>
       </c>
       <c r="E7" s="0">
-        <v>0.0055862153943264555</v>
+        <v>0.0054851414691450663</v>
       </c>
       <c r="F7" s="0">
-        <v>0.0040781770320104226</v>
+        <v>0.0041619628322821589</v>
       </c>
       <c r="G7" s="0">
-        <v>0.0052530527720142254</v>
+        <v>0.0053194218743548623</v>
       </c>
       <c r="H7" s="0">
-        <v>0.0064279285120180281</v>
+        <v>0.0064768809164275658</v>
       </c>
       <c r="I7" s="0">
-        <v>0.00027155040252839838</v>
+        <v>-0.002228234929067094</v>
       </c>
       <c r="J7" s="0">
-        <v>0.0044068818617010635</v>
+        <v>0.0018434578811310348</v>
       </c>
       <c r="K7" s="0">
-        <v>0.0085422133208737285</v>
+        <v>0.0059151506913291641</v>
       </c>
       <c r="L7" s="0">
-        <v>0.70278533604578541</v>
+        <v>0.70194360142111323</v>
       </c>
       <c r="M7" s="0">
-        <v>0.79850163581021905</v>
+        <v>0.79619635160149427</v>
       </c>
       <c r="N7" s="0">
-        <v>0.89421793557465268</v>
+        <v>0.89044910178187531</v>
       </c>
       <c r="O7" s="0">
-        <v>-0.018952320902739198</v>
+        <v>-0.018557007261303629</v>
       </c>
       <c r="P7" s="0">
-        <v>-0.011841869990002401</v>
+        <v>-0.011553757204413794</v>
       </c>
       <c r="Q7" s="0">
-        <v>-0.0047314190772656034</v>
+        <v>-0.0045505071475239606</v>
       </c>
       <c r="R7" s="0">
-        <v>0.77898103649489581</v>
+        <v>0.77862025004384783</v>
       </c>
       <c r="S7" s="0">
-        <v>0.78682558917616452</v>
+        <v>0.78634578243416242</v>
       </c>
       <c r="T7" s="0">
-        <v>0.79467014185743323</v>
+        <v>0.79407131482447702</v>
       </c>
       <c r="U7" s="0">
-        <v>0.0015050694703876411</v>
+        <v>0.001446005129037144</v>
       </c>
       <c r="V7" s="0">
-        <v>0.0038030469757695216</v>
+        <v>0.0037102077977696412</v>
       </c>
       <c r="W7" s="0">
-        <v>0.0061010244811514017</v>
+        <v>0.0059744104665021385</v>
       </c>
       <c r="X7" s="0">
-        <v>3.6851712517926383</v>
+        <v>3.3119650457310526</v>
       </c>
       <c r="Y7" s="0">
-        <v>4.9176338688631418</v>
+        <v>4.5227503167151788</v>
       </c>
       <c r="Z7" s="0">
-        <v>6.1500964859336449</v>
+        <v>5.733535587699305</v>
       </c>
     </row>
     <row r="8">
@@ -832,76 +838,76 @@
         <v>53</v>
       </c>
       <c r="C8" s="0">
-        <v>0.0068534550133549348</v>
+        <v>0.0069700048010795171</v>
       </c>
       <c r="D8" s="0">
-        <v>0.012279402550980865</v>
+        <v>0.01181156124852235</v>
       </c>
       <c r="E8" s="0">
-        <v>0.017705350088606797</v>
+        <v>0.016653117695965183</v>
       </c>
       <c r="F8" s="0">
-        <v>0.0050717172506346926</v>
+        <v>0.0054140082536002308</v>
       </c>
       <c r="G8" s="0">
-        <v>0.0068211480226148952</v>
+        <v>0.0069723927332626511</v>
       </c>
       <c r="H8" s="0">
-        <v>0.0085705787945950969</v>
+        <v>0.0085307772129250715</v>
       </c>
       <c r="I8" s="0">
-        <v>0.008981244144589385</v>
+        <v>0.0077836856953994154</v>
       </c>
       <c r="J8" s="0">
-        <v>0.013663561011072847</v>
+        <v>0.011963362763196005</v>
       </c>
       <c r="K8" s="0">
-        <v>0.018345877877556309</v>
+        <v>0.016143039830992592</v>
       </c>
       <c r="L8" s="0">
-        <v>0.58927876416125391</v>
+        <v>0.59546726857852428</v>
       </c>
       <c r="M8" s="0">
-        <v>0.70008314655488713</v>
+        <v>0.69415882618089953</v>
       </c>
       <c r="N8" s="0">
-        <v>0.81088752894852034</v>
+        <v>0.79285038378327477</v>
       </c>
       <c r="O8" s="0">
-        <v>-0.013660012919559931</v>
+        <v>-0.012018277981715609</v>
       </c>
       <c r="P8" s="0">
-        <v>-0.0052636664842404006</v>
+        <v>-0.004539023566787306</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.0031326799510791288</v>
+        <v>0.0029402308481409978</v>
       </c>
       <c r="R8" s="0">
-        <v>0.78029544122381034</v>
+        <v>0.78017681519718207</v>
       </c>
       <c r="S8" s="0">
-        <v>0.78886078505949231</v>
+        <v>0.78780688051949555</v>
       </c>
       <c r="T8" s="0">
-        <v>0.79742612889517428</v>
+        <v>0.79543694584180902</v>
       </c>
       <c r="U8" s="0">
-        <v>0.0088186130794424</v>
+        <v>0.0089237181755280198</v>
       </c>
       <c r="V8" s="0">
-        <v>0.012726884352763</v>
+        <v>0.01240792014815871</v>
       </c>
       <c r="W8" s="0">
-        <v>0.0166351556260836</v>
+        <v>0.015892122120789401</v>
       </c>
       <c r="X8" s="0">
-        <v>-0.55063647184492948</v>
+        <v>-1.3456772047800345</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.32535340788109562</v>
+        <v>-0.57271822646728232</v>
       </c>
       <c r="Z8" s="0">
-        <v>1.2013432876071208</v>
+        <v>0.20024075184546997</v>
       </c>
     </row>
     <row r="9">
@@ -909,79 +915,79 @@
         <v>3</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C9" s="0">
-        <v>0.0017942013806805258</v>
+        <v>0.0018027904781274108</v>
       </c>
       <c r="D9" s="0">
-        <v>0.0049279826277870663</v>
+        <v>0.0049243156706230765</v>
       </c>
       <c r="E9" s="0">
-        <v>0.0080617638748936068</v>
+        <v>0.0080458408631187417</v>
       </c>
       <c r="F9" s="0">
-        <v>-0.0040303722293669065</v>
+        <v>-0.0040293616366065266</v>
       </c>
       <c r="G9" s="0">
-        <v>-0.0038546269556382234</v>
+        <v>-0.0038543740830051035</v>
       </c>
       <c r="H9" s="0">
-        <v>-0.0036788816819095399</v>
+        <v>-0.0036793865294036804</v>
       </c>
       <c r="I9" s="0">
-        <v>-0.00075473252190358365</v>
+        <v>-0.00075448889298558347</v>
       </c>
       <c r="J9" s="0">
-        <v>-0.00057434369323037539</v>
+        <v>-0.00057488527874165456</v>
       </c>
       <c r="K9" s="0">
-        <v>-0.00039395486455716719</v>
+        <v>-0.00039528166449772566</v>
       </c>
       <c r="L9" s="0">
-        <v>0.69783003903359908</v>
+        <v>0.69782118647577562</v>
       </c>
       <c r="M9" s="0">
-        <v>0.72005208993809344</v>
+        <v>0.71994953808205442</v>
       </c>
       <c r="N9" s="0">
-        <v>0.7422741408425878</v>
+        <v>0.74207788968833321</v>
       </c>
       <c r="O9" s="0">
-        <v>-0.026785800763973466</v>
+        <v>-0.026765599368661949</v>
       </c>
       <c r="P9" s="0">
-        <v>-0.024520965112172749</v>
+        <v>-0.024510271616848423</v>
       </c>
       <c r="Q9" s="0">
-        <v>-0.022256129460372032</v>
+        <v>-0.022254943865034897</v>
       </c>
       <c r="R9" s="0">
-        <v>0.77442517538572353</v>
+        <v>0.77443982853653381</v>
       </c>
       <c r="S9" s="0">
-        <v>0.77920506672699663</v>
+        <v>0.77920057005259813</v>
       </c>
       <c r="T9" s="0">
-        <v>0.78398495806826973</v>
+        <v>0.78396131156866244</v>
       </c>
       <c r="U9" s="0">
-        <v>0.0072576562839515068</v>
+        <v>0.0072599912910900934</v>
       </c>
       <c r="V9" s="0">
-        <v>0.0077291883226053059</v>
+        <v>0.0077296229795930762</v>
       </c>
       <c r="W9" s="0">
-        <v>0.0082007203612591058</v>
+        <v>0.0081992546680960589</v>
       </c>
       <c r="X9" s="0">
-        <v>-2.5487075181983299</v>
+        <v>-2.8773348992718235</v>
       </c>
       <c r="Y9" s="0">
-        <v>-2.5361546478538291</v>
+        <v>-2.8648359067501326</v>
       </c>
       <c r="Z9" s="0">
-        <v>-2.5236017775093282</v>
+        <v>-2.8523369142284416</v>
       </c>
     </row>
     <row r="10">
@@ -992,76 +998,76 @@
         <v>55</v>
       </c>
       <c r="C10" s="0">
-        <v>0.015066001204067113</v>
+        <v>0.014987020904183551</v>
       </c>
       <c r="D10" s="0">
-        <v>0.017453093079194761</v>
+        <v>0.017453219287315219</v>
       </c>
       <c r="E10" s="0">
-        <v>0.01984018495432241</v>
+        <v>0.019919417670446887</v>
       </c>
       <c r="F10" s="0">
-        <v>0.0002072001366418177</v>
+        <v>0.00016384533742490391</v>
       </c>
       <c r="G10" s="0">
-        <v>0.00032660178181571204</v>
+        <v>0.00028708628221050885</v>
       </c>
       <c r="H10" s="0">
-        <v>0.00044600342698960637</v>
+        <v>0.00041032722699611379</v>
       </c>
       <c r="I10" s="0">
-        <v>0.00054308285957090151</v>
+        <v>0.00054522419941702106</v>
       </c>
       <c r="J10" s="0">
-        <v>0.00066118932857755293</v>
+        <v>0.00066714286968259365</v>
       </c>
       <c r="K10" s="0">
-        <v>0.00077929579758420436</v>
+        <v>0.00078906153994816623</v>
       </c>
       <c r="L10" s="0">
-        <v>0.74149050990589793</v>
+        <v>0.74302102857031405</v>
       </c>
       <c r="M10" s="0">
-        <v>0.74526116809034293</v>
+        <v>0.74691323012512734</v>
       </c>
       <c r="N10" s="0">
-        <v>0.74903182627478793</v>
+        <v>0.75080543167994063</v>
       </c>
       <c r="O10" s="0">
-        <v>-0.018205907468556687</v>
+        <v>-0.018494925675459968</v>
       </c>
       <c r="P10" s="0">
-        <v>-0.017692543409439644</v>
+        <v>-0.017965113766519277</v>
       </c>
       <c r="Q10" s="0">
-        <v>-0.0171791793503226</v>
+        <v>-0.017435301857578585</v>
       </c>
       <c r="R10" s="0">
-        <v>0.8036029326965779</v>
+        <v>0.79768091883926162</v>
       </c>
       <c r="S10" s="0">
-        <v>0.8102743925759831</v>
+        <v>0.80456684320298355</v>
       </c>
       <c r="T10" s="0">
-        <v>0.81694585245538831</v>
+        <v>0.81145276756670548</v>
       </c>
       <c r="U10" s="0">
-        <v>0.0064218290245111019</v>
+        <v>0.0063407369623080453</v>
       </c>
       <c r="V10" s="0">
-        <v>0.0068712116659131817</v>
+        <v>0.0068046413859159573</v>
       </c>
       <c r="W10" s="0">
-        <v>0.0073205943073152615</v>
+        <v>0.0072685458095238693</v>
       </c>
       <c r="X10" s="0">
-        <v>-2.2495209567008896</v>
+        <v>-2.4940185217612658</v>
       </c>
       <c r="Y10" s="0">
-        <v>-2.243742908057599</v>
+        <v>-2.4880551193355611</v>
       </c>
       <c r="Z10" s="0">
-        <v>-2.2379648594143085</v>
+        <v>-2.4820917169098564</v>
       </c>
     </row>
     <row r="11">
@@ -1069,79 +1075,79 @@
         <v>3</v>
       </c>
       <c r="B11" s="0" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C11" s="0">
-        <v>0.00035511819866908268</v>
+        <v>-0.0020000958384486294</v>
       </c>
       <c r="D11" s="0">
-        <v>0.0084038983200518235</v>
+        <v>0.0055448989586143723</v>
       </c>
       <c r="E11" s="0">
-        <v>0.016452678441434564</v>
+        <v>0.013089893755677373</v>
       </c>
       <c r="F11" s="0">
-        <v>-0.0015430138774729378</v>
+        <v>-0.0022442956168592159</v>
       </c>
       <c r="G11" s="0">
-        <v>0.0020749462179833382</v>
+        <v>0.0011428926872617585</v>
       </c>
       <c r="H11" s="0">
-        <v>0.0056929063134396139</v>
+        <v>0.0045300809913827326</v>
       </c>
       <c r="I11" s="0">
-        <v>-0.044236891013769111</v>
+        <v>-0.043766020114319466</v>
       </c>
       <c r="J11" s="0">
-        <v>-0.034906282925724667</v>
+        <v>-0.034906579133606668</v>
       </c>
       <c r="K11" s="0">
-        <v>-0.02557567483768022</v>
+        <v>-0.026047138152893869</v>
       </c>
       <c r="L11" s="0">
-        <v>0.55291448488700412</v>
+        <v>0.55730249755974992</v>
       </c>
       <c r="M11" s="0">
-        <v>0.64924788530292643</v>
+        <v>0.64748914017707804</v>
       </c>
       <c r="N11" s="0">
-        <v>0.74558128571884874</v>
+        <v>0.73767578279440615</v>
       </c>
       <c r="O11" s="0">
-        <v>-0.015486530268796483</v>
+        <v>-0.016354163973378535</v>
       </c>
       <c r="P11" s="0">
-        <v>-0.0047401200002335801</v>
+        <v>-0.0063056398934803904</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.0060062902683293241</v>
+        <v>0.0037428841864177529</v>
       </c>
       <c r="R11" s="0">
-        <v>0.77440434763983779</v>
+        <v>0.77378326745051596</v>
       </c>
       <c r="S11" s="0">
-        <v>0.78674455413216737</v>
+        <v>0.7853412717454592</v>
       </c>
       <c r="T11" s="0">
-        <v>0.79908476062449696</v>
+        <v>0.79689927604040245</v>
       </c>
       <c r="U11" s="0">
-        <v>0.003826008476653567</v>
+        <v>-0.0010030596185734066</v>
       </c>
       <c r="V11" s="0">
-        <v>0.011562221959015776</v>
+        <v>0.0062145309942639119</v>
       </c>
       <c r="W11" s="0">
-        <v>0.019298435441377985</v>
+        <v>0.01343212160710123</v>
       </c>
       <c r="X11" s="0">
-        <v>-5.6055896545639943</v>
+        <v>-8.6764608254806177</v>
       </c>
       <c r="Y11" s="0">
-        <v>-4.175388897900489</v>
+        <v>-7.4099257998149062</v>
       </c>
       <c r="Z11" s="0">
-        <v>-2.7451881412369841</v>
+        <v>-6.1433907741491955</v>
       </c>
     </row>
     <row r="12">
@@ -1152,76 +1158,76 @@
         <v>53</v>
       </c>
       <c r="C12" s="0">
-        <v>0.013728402161449845</v>
+        <v>0.013749767804785814</v>
       </c>
       <c r="D12" s="0">
-        <v>0.017453053014123313</v>
+        <v>0.017452867192827987</v>
       </c>
       <c r="E12" s="0">
-        <v>0.021177703866796779</v>
+        <v>0.021155966580870159</v>
       </c>
       <c r="F12" s="0">
-        <v>0.0044468456774554421</v>
+        <v>0.0044490277613636747</v>
       </c>
       <c r="G12" s="0">
-        <v>0.004684941087724004</v>
+        <v>0.0046857049912841812</v>
       </c>
       <c r="H12" s="0">
-        <v>0.004923036497992566</v>
+        <v>0.0049223822212046877</v>
       </c>
       <c r="I12" s="0">
-        <v>0.0012604276570940918</v>
+        <v>0.001264306913898989</v>
       </c>
       <c r="J12" s="0">
-        <v>0.001501391286618686</v>
+        <v>0.0015038264445229768</v>
       </c>
       <c r="K12" s="0">
-        <v>0.0017423549161432802</v>
+        <v>0.0017433459751469646</v>
       </c>
       <c r="L12" s="0">
-        <v>0.84120111660621277</v>
+        <v>0.84119649555797471</v>
       </c>
       <c r="M12" s="0">
-        <v>0.86074995576353663</v>
+        <v>0.86062699183111557</v>
       </c>
       <c r="N12" s="0">
-        <v>0.8802987949208605</v>
+        <v>0.88005748810425644</v>
       </c>
       <c r="O12" s="0">
-        <v>-0.021698266454835573</v>
+        <v>-0.021672748224592121</v>
       </c>
       <c r="P12" s="0">
-        <v>-0.019599007762946929</v>
+        <v>-0.019586067267221233</v>
       </c>
       <c r="Q12" s="0">
-        <v>-0.017499749071058286</v>
+        <v>-0.017499386309850346</v>
       </c>
       <c r="R12" s="0">
-        <v>0.76088049109291778</v>
+        <v>0.76095754164500928</v>
       </c>
       <c r="S12" s="0">
-        <v>0.7668542958809812</v>
+        <v>0.76689715329836439</v>
       </c>
       <c r="T12" s="0">
-        <v>0.77282810066904462</v>
+        <v>0.77283676495171949</v>
       </c>
       <c r="U12" s="0">
-        <v>0.0049189025791670869</v>
+        <v>0.0049184342184794057</v>
       </c>
       <c r="V12" s="0">
-        <v>0.0056680964652170603</v>
+        <v>0.0056632751207881197</v>
       </c>
       <c r="W12" s="0">
-        <v>0.0064172903512670337</v>
+        <v>0.0064081160230968336</v>
       </c>
       <c r="X12" s="0">
-        <v>-2.4467085528352106</v>
+        <v>-2.7687512495058724</v>
       </c>
       <c r="Y12" s="0">
-        <v>-2.4305529980949072</v>
+        <v>-2.7526916301701827</v>
       </c>
       <c r="Z12" s="0">
-        <v>-2.4143974433546038</v>
+        <v>-2.736632010834493</v>
       </c>
     </row>
     <row r="13">
@@ -1232,76 +1238,76 @@
         <v>53</v>
       </c>
       <c r="C13" s="0">
-        <v>0.0012722492832160526</v>
+        <v>0.0020295101938568681</v>
       </c>
       <c r="D13" s="0">
-        <v>0.0059305565412257613</v>
+        <v>0.0068421004462719285</v>
       </c>
       <c r="E13" s="0">
-        <v>0.01058886379923547</v>
+        <v>0.011654690698686989</v>
       </c>
       <c r="F13" s="0">
-        <v>0.0019310986190469301</v>
+        <v>0.001870828981281848</v>
       </c>
       <c r="G13" s="0">
-        <v>0.0021468451404757952</v>
+        <v>0.00209390037936228</v>
       </c>
       <c r="H13" s="0">
-        <v>0.0023625916619046602</v>
+        <v>0.0023169717774427119</v>
       </c>
       <c r="I13" s="0">
-        <v>0.0011281690999726673</v>
+        <v>0.0011251438653505216</v>
       </c>
       <c r="J13" s="0">
-        <v>0.0013377667609018424</v>
+        <v>0.0013418756092324216</v>
       </c>
       <c r="K13" s="0">
-        <v>0.0015473644218310175</v>
+        <v>0.0015586073531143217</v>
       </c>
       <c r="L13" s="0">
-        <v>0.84748827939274007</v>
+        <v>0.84937047335961635</v>
       </c>
       <c r="M13" s="0">
-        <v>0.85455199770640511</v>
+        <v>0.85667226101843497</v>
       </c>
       <c r="N13" s="0">
-        <v>0.86161571602007014</v>
+        <v>0.86397404867725358</v>
       </c>
       <c r="O13" s="0">
-        <v>-0.027033010298571456</v>
+        <v>-0.027417578680521491</v>
       </c>
       <c r="P13" s="0">
-        <v>-0.02604416392875419</v>
+        <v>-0.02639587425238393</v>
       </c>
       <c r="Q13" s="0">
-        <v>-0.025055317558936925</v>
+        <v>-0.025374169824246368</v>
       </c>
       <c r="R13" s="0">
-        <v>0.74831028516950326</v>
+        <v>0.74157247380194347</v>
       </c>
       <c r="S13" s="0">
-        <v>0.76374868423740139</v>
+        <v>0.75751903127035902</v>
       </c>
       <c r="T13" s="0">
-        <v>0.77918708330529951</v>
+        <v>0.77346558873877458</v>
       </c>
       <c r="U13" s="0">
-        <v>0.00068765510575443712</v>
+        <v>0.00075125347054934625</v>
       </c>
       <c r="V13" s="0">
-        <v>0.0016059795474518063</v>
+        <v>0.0016993475727075788</v>
       </c>
       <c r="W13" s="0">
-        <v>0.0025243039891491756</v>
+        <v>0.0026474416748658112</v>
       </c>
       <c r="X13" s="0">
-        <v>-2.2419129194707099</v>
+        <v>-2.4511540975827546</v>
       </c>
       <c r="Y13" s="0">
-        <v>-2.2308075753320429</v>
+        <v>-2.4396733941288651</v>
       </c>
       <c r="Z13" s="0">
-        <v>-2.2197022311933759</v>
+        <v>-2.4281926906749756</v>
       </c>
     </row>
     <row r="14">
@@ -1312,76 +1318,76 @@
         <v>53</v>
       </c>
       <c r="C14" s="0">
-        <v>0.0093902295229091864</v>
+        <v>0.0091923806212589661</v>
       </c>
       <c r="D14" s="0">
-        <v>0.017453292509991086</v>
+        <v>0.017453292508735788</v>
       </c>
       <c r="E14" s="0">
-        <v>0.025516355497072985</v>
+        <v>0.025714204396212609</v>
       </c>
       <c r="F14" s="0">
-        <v>0.0074667149251210832</v>
+        <v>0.0074991456350755898</v>
       </c>
       <c r="G14" s="0">
-        <v>0.0086875630516538086</v>
+        <v>0.0087494018471908283</v>
       </c>
       <c r="H14" s="0">
-        <v>0.0099084111781865339</v>
+        <v>0.0099996580593060668</v>
       </c>
       <c r="I14" s="0">
-        <v>-0.0010316651615048641</v>
+        <v>-0.0010175072038584769</v>
       </c>
       <c r="J14" s="0">
-        <v>0.00018122850610010301</v>
+        <v>0.00022476327431824708</v>
       </c>
       <c r="K14" s="0">
-        <v>0.0013941221737050703</v>
+        <v>0.0014670337524949712</v>
       </c>
       <c r="L14" s="0">
-        <v>0.72456373200909785</v>
+        <v>0.72418977548263463</v>
       </c>
       <c r="M14" s="0">
-        <v>0.73780437132836851</v>
+        <v>0.73776300353514501</v>
       </c>
       <c r="N14" s="0">
-        <v>0.75104501064763918</v>
+        <v>0.75133623158765539</v>
       </c>
       <c r="O14" s="0">
-        <v>-0.0015889110149982122</v>
+        <v>-0.0015289648272463886</v>
       </c>
       <c r="P14" s="0">
-        <v>0.0012081500407561377</v>
+        <v>0.0013360698982208044</v>
       </c>
       <c r="Q14" s="0">
-        <v>0.0040052110965104878</v>
+        <v>0.0042011046236879977</v>
       </c>
       <c r="R14" s="0">
-        <v>0.9488935422257907</v>
+        <v>0.95162332330564736</v>
       </c>
       <c r="S14" s="0">
-        <v>0.98359906129571495</v>
+        <v>0.9871899207360556</v>
       </c>
       <c r="T14" s="0">
-        <v>1.0183045803656392</v>
+        <v>1.022756518166464</v>
       </c>
       <c r="U14" s="0">
-        <v>0.0067700833157045264</v>
+        <v>0.0067367378787993835</v>
       </c>
       <c r="V14" s="0">
-        <v>0.0093699191027466055</v>
+        <v>0.0094002042158772298</v>
       </c>
       <c r="W14" s="0">
-        <v>0.011969754889788685</v>
+        <v>0.012063670552955076</v>
       </c>
       <c r="X14" s="0">
-        <v>-1.7228030920777149</v>
+        <v>-1.9201667184368756</v>
       </c>
       <c r="Y14" s="0">
-        <v>-1.6826548463312878</v>
+        <v>-1.8790154186096202</v>
       </c>
       <c r="Z14" s="0">
-        <v>-1.6425066005848608</v>
+        <v>-1.8378641187823648</v>
       </c>
     </row>
     <row r="15">
@@ -1389,79 +1395,79 @@
         <v>4</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C15" s="0">
-        <v>0.0024783860419980552</v>
+        <v>0.0024644542704711147</v>
       </c>
       <c r="D15" s="0">
-        <v>0.0066867881125117785</v>
+        <v>0.0066766920873522883</v>
       </c>
       <c r="E15" s="0">
-        <v>0.010895190183025502</v>
+        <v>0.010888929904233461</v>
       </c>
       <c r="F15" s="0">
-        <v>-0.019954418902737775</v>
+        <v>-0.019955758715963629</v>
       </c>
       <c r="G15" s="0">
-        <v>-0.017453292519094544</v>
+        <v>-0.017453292519350169</v>
       </c>
       <c r="H15" s="0">
-        <v>-0.014952166135451313</v>
+        <v>-0.014950826322736711</v>
       </c>
       <c r="I15" s="0">
-        <v>-0.0083366641378773611</v>
+        <v>-0.0091002942889792347</v>
       </c>
       <c r="J15" s="0">
-        <v>-0.0015036290088107523</v>
+        <v>-0.0022748567569120222</v>
       </c>
       <c r="K15" s="0">
-        <v>0.0053294061202558574</v>
+        <v>0.0045505807751551894</v>
       </c>
       <c r="L15" s="0">
-        <v>0.69732696769667646</v>
+        <v>0.69722658295694906</v>
       </c>
       <c r="M15" s="0">
-        <v>0.76145456642769938</v>
+        <v>0.76140039851818753</v>
       </c>
       <c r="N15" s="0">
-        <v>0.82558216515872229</v>
+        <v>0.825574214079426</v>
       </c>
       <c r="O15" s="0">
-        <v>-0.05966384806681134</v>
+        <v>-0.059662729516551744</v>
       </c>
       <c r="P15" s="0">
-        <v>-0.051911511549711298</v>
+        <v>-0.051905228472134003</v>
       </c>
       <c r="Q15" s="0">
-        <v>-0.044159175032611256</v>
+        <v>-0.044147727427716263</v>
       </c>
       <c r="R15" s="0">
-        <v>0.79254611284377796</v>
+        <v>0.79251780840691122</v>
       </c>
       <c r="S15" s="0">
-        <v>0.79952123329233127</v>
+        <v>0.79949247265146939</v>
       </c>
       <c r="T15" s="0">
-        <v>0.80649635374088458</v>
+        <v>0.80646713689602756</v>
       </c>
       <c r="U15" s="0">
-        <v>0.0067784424470578725</v>
+        <v>0.0067619811924455433</v>
       </c>
       <c r="V15" s="0">
-        <v>0.011788402444087786</v>
+        <v>0.011774332923553935</v>
       </c>
       <c r="W15" s="0">
-        <v>0.016798362441117699</v>
+        <v>0.016786684654662327</v>
       </c>
       <c r="X15" s="0">
-        <v>0.0473358036996816</v>
+        <v>-0.1645089730092868</v>
       </c>
       <c r="Y15" s="0">
-        <v>1.0804414902960424</v>
+        <v>0.87030144435966528</v>
       </c>
       <c r="Z15" s="0">
-        <v>2.1135471768924035</v>
+        <v>1.9051118617286174</v>
       </c>
     </row>
     <row r="16">
@@ -1469,79 +1475,79 @@
         <v>5</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C16" s="0">
-        <v>0.0097390447771719627</v>
+        <v>0.0097316398432091555</v>
       </c>
       <c r="D16" s="0">
-        <v>0.013590900353462752</v>
+        <v>0.013594150541322382</v>
       </c>
       <c r="E16" s="0">
-        <v>0.017442755929753539</v>
+        <v>0.017456661239435609</v>
       </c>
       <c r="F16" s="0">
-        <v>1.5209539473288168e-05</v>
+        <v>1.4852856724011218e-05</v>
       </c>
       <c r="G16" s="0">
-        <v>0.00031128451772305632</v>
+        <v>0.00031165539084955561</v>
       </c>
       <c r="H16" s="0">
-        <v>0.00060735949597282447</v>
+        <v>0.00060845792497509995</v>
       </c>
       <c r="I16" s="0">
-        <v>-0.00035515212525024861</v>
+        <v>-0.0003611127062923965</v>
       </c>
       <c r="J16" s="0">
-        <v>-5.6529827725702365e-05</v>
+        <v>-6.1757458684381898e-05</v>
       </c>
       <c r="K16" s="0">
-        <v>0.00024209246979884388</v>
+        <v>0.00023759778892363273</v>
       </c>
       <c r="L16" s="0">
-        <v>0.66495523276232294</v>
+        <v>0.66494784201922341</v>
       </c>
       <c r="M16" s="0">
-        <v>0.69967035172557712</v>
+        <v>0.69974574197748762</v>
       </c>
       <c r="N16" s="0">
-        <v>0.73438547068883131</v>
+        <v>0.73454364193575183</v>
       </c>
       <c r="O16" s="0">
-        <v>-0.014113203908069029</v>
+        <v>-0.014127257741284831</v>
       </c>
       <c r="P16" s="0">
-        <v>-0.010932738418181348</v>
+        <v>-0.010939062787582247</v>
       </c>
       <c r="Q16" s="0">
-        <v>-0.0077522729282936669</v>
+        <v>-0.0077508678338796631</v>
       </c>
       <c r="R16" s="0">
-        <v>0.7812671007793992</v>
+        <v>0.78123895950787825</v>
       </c>
       <c r="S16" s="0">
-        <v>0.78742541950867606</v>
+        <v>0.78741427507526096</v>
       </c>
       <c r="T16" s="0">
-        <v>0.79358373823795292</v>
+        <v>0.79358959064264367</v>
       </c>
       <c r="U16" s="0">
-        <v>0.010811858433241226</v>
+        <v>0.010810697763371074</v>
       </c>
       <c r="V16" s="0">
-        <v>0.011555665703682211</v>
+        <v>0.01155645983666859</v>
       </c>
       <c r="W16" s="0">
-        <v>0.012299472974123196</v>
+        <v>0.012302221909966106</v>
       </c>
       <c r="X16" s="0">
-        <v>-2.6337508537214789</v>
+        <v>-3.067130917807412</v>
       </c>
       <c r="Y16" s="0">
-        <v>-2.6107371890713376</v>
+        <v>-3.0440595302561713</v>
       </c>
       <c r="Z16" s="0">
-        <v>-2.5877235244211962</v>
+        <v>-3.0209881427049306</v>
       </c>
     </row>
     <row r="17">
@@ -1552,76 +1558,76 @@
         <v>53</v>
       </c>
       <c r="C17" s="0">
-        <v>0.013876988732866134</v>
+        <v>0.013310533353739402</v>
       </c>
       <c r="D17" s="0">
-        <v>0.017453289952799465</v>
+        <v>0.017453289918801965</v>
       </c>
       <c r="E17" s="0">
-        <v>0.021029591172732794</v>
+        <v>0.021596046483864529</v>
       </c>
       <c r="F17" s="0">
-        <v>-0.0045090309278879668</v>
+        <v>-0.0045530209645435983</v>
       </c>
       <c r="G17" s="0">
-        <v>-0.0043206935928526832</v>
+        <v>-0.0043346146288625728</v>
       </c>
       <c r="H17" s="0">
-        <v>-0.0041323562578173996</v>
+        <v>-0.0041162082931815473</v>
       </c>
       <c r="I17" s="0">
-        <v>0.0024920462341977124</v>
+        <v>0.0024836095893987112</v>
       </c>
       <c r="J17" s="0">
-        <v>0.0026763187849215379</v>
+        <v>0.0026973119449674628</v>
       </c>
       <c r="K17" s="0">
-        <v>0.0028605913356453635</v>
+        <v>0.0029110143005362144</v>
       </c>
       <c r="L17" s="0">
-        <v>0.74478958369614989</v>
+        <v>0.74530455747567659</v>
       </c>
       <c r="M17" s="0">
-        <v>0.75003897887505055</v>
+        <v>0.75139412274690753</v>
       </c>
       <c r="N17" s="0">
-        <v>0.75528837405395122</v>
+        <v>0.75748368801813848</v>
       </c>
       <c r="O17" s="0">
-        <v>-0.026364981843619965</v>
+        <v>-0.026622346574208419</v>
       </c>
       <c r="P17" s="0">
-        <v>-0.025735623876853589</v>
+        <v>-0.025892731373221494</v>
       </c>
       <c r="Q17" s="0">
-        <v>-0.025106265910087213</v>
+        <v>-0.02516311617223457</v>
       </c>
       <c r="R17" s="0">
-        <v>0.59536710463127995</v>
+        <v>0.58964458759895544</v>
       </c>
       <c r="S17" s="0">
-        <v>0.6093845341730777</v>
+        <v>0.60590844645961073</v>
       </c>
       <c r="T17" s="0">
-        <v>0.62340196371487544</v>
+        <v>0.62217230532026602</v>
       </c>
       <c r="U17" s="0">
-        <v>0.002103521496251841</v>
+        <v>0.0019548726130575018</v>
       </c>
       <c r="V17" s="0">
-        <v>0.0026532628568017437</v>
+        <v>0.0025917237788110684</v>
       </c>
       <c r="W17" s="0">
-        <v>0.0032030042173516464</v>
+        <v>0.003228574944564635</v>
       </c>
       <c r="X17" s="0">
-        <v>-2.5236229712032472</v>
+        <v>-2.8788134467517326</v>
       </c>
       <c r="Y17" s="0">
-        <v>-2.5127828485020229</v>
+        <v>-2.8662509110743453</v>
       </c>
       <c r="Z17" s="0">
-        <v>-2.5019427258007987</v>
+        <v>-2.853688375396958</v>
       </c>
     </row>
     <row r="18">
@@ -1632,76 +1638,76 @@
         <v>53</v>
       </c>
       <c r="C18" s="0">
-        <v>-0.0024677097337426268</v>
+        <v>-0.0043209777401085683</v>
       </c>
       <c r="D18" s="0">
-        <v>0.0020231623529237929</v>
+        <v>0.00060258815506627095</v>
       </c>
       <c r="E18" s="0">
-        <v>0.0065140344395902125</v>
+        <v>0.00552615405024111</v>
       </c>
       <c r="F18" s="0">
-        <v>-0.0068910294675713999</v>
+        <v>-0.0070531080568805218</v>
       </c>
       <c r="G18" s="0">
-        <v>-0.0066940796902513963</v>
+        <v>-0.0068356417352086986</v>
       </c>
       <c r="H18" s="0">
-        <v>-0.0064971299129313927</v>
+        <v>-0.0066181754135368753</v>
       </c>
       <c r="I18" s="0">
-        <v>-0.0016617549681861824</v>
+        <v>-0.0016785326795013945</v>
       </c>
       <c r="J18" s="0">
-        <v>-0.0014733386103622213</v>
+        <v>-0.0014705709611087284</v>
       </c>
       <c r="K18" s="0">
-        <v>-0.0012849222525382602</v>
+        <v>-0.0012626092427160624</v>
       </c>
       <c r="L18" s="0">
-        <v>0.82591757463104265</v>
+        <v>0.83401294829620543</v>
       </c>
       <c r="M18" s="0">
-        <v>0.83134205631035518</v>
+        <v>0.83999852569874789</v>
       </c>
       <c r="N18" s="0">
-        <v>0.83676653798966771</v>
+        <v>0.84598410310129035</v>
       </c>
       <c r="O18" s="0">
-        <v>-0.037108233408412551</v>
+        <v>-0.038261616303055669</v>
       </c>
       <c r="P18" s="0">
-        <v>-0.036455505400705648</v>
+        <v>-0.037541708725448549</v>
       </c>
       <c r="Q18" s="0">
-        <v>-0.035802777392998746</v>
+        <v>-0.036821801147841428</v>
       </c>
       <c r="R18" s="0">
-        <v>0.68638193617401388</v>
+        <v>0.67102928274670382</v>
       </c>
       <c r="S18" s="0">
-        <v>0.70760110290227774</v>
+        <v>0.69450654909140552</v>
       </c>
       <c r="T18" s="0">
-        <v>0.72882026963054158</v>
+        <v>0.71798381543610723</v>
       </c>
       <c r="U18" s="0">
-        <v>0.0076351858156501508</v>
+        <v>0.0073352140393774515</v>
       </c>
       <c r="V18" s="0">
-        <v>0.0083043612282990929</v>
+        <v>0.0080698138965137022</v>
       </c>
       <c r="W18" s="0">
-        <v>0.0089735366409480349</v>
+        <v>0.0088044137536499537</v>
       </c>
       <c r="X18" s="0">
-        <v>-2.416987890539481</v>
+        <v>-2.7770271674878528</v>
       </c>
       <c r="Y18" s="0">
-        <v>-2.4040413379906571</v>
+        <v>-2.7627424398204736</v>
       </c>
       <c r="Z18" s="0">
-        <v>-2.3910947854418332</v>
+        <v>-2.7484577121530944</v>
       </c>
     </row>
     <row r="19">
@@ -1738,76 +1744,76 @@
       </c>
       <c r="B20" s="0"/>
       <c r="C20" s="0">
-        <v>0.0055527456464491663</v>
+        <v>0.0054131145979337278</v>
       </c>
       <c r="D20" s="0">
-        <v>0.010605461050258232</v>
+        <v>0.010328563161012804</v>
       </c>
       <c r="E20" s="0">
-        <v>0.015140339223298865</v>
+        <v>0.015009643922906168</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0010260872192706565</v>
+        <v>0.0010405461014561586</v>
       </c>
       <c r="G20" s="0">
-        <v>0.0018382159352646442</v>
+        <v>0.0018298389051768296</v>
       </c>
       <c r="H20" s="0">
-        <v>0.0027740999830033644</v>
+        <v>0.002752442033597635</v>
       </c>
       <c r="I20" s="0">
-        <v>-0.001304865421470535</v>
+        <v>-0.0026245409914786148</v>
       </c>
       <c r="J20" s="0">
-        <v>0.0010688681009061649</v>
+        <v>-0.00030878560190745932</v>
       </c>
       <c r="K20" s="0">
-        <v>0.0034725038343876315</v>
+        <v>0.0019752088567687896</v>
       </c>
       <c r="L20" s="0">
-        <v>0.67160014611144347</v>
+        <v>0.68906953389862025</v>
       </c>
       <c r="M20" s="0">
-        <v>0.71799953858719179</v>
+        <v>0.71528495188756458</v>
       </c>
       <c r="N20" s="0">
-        <v>0.7603718417621268</v>
+        <v>0.77169269581906375</v>
       </c>
       <c r="O20" s="0">
-        <v>-0.017203112902425263</v>
+        <v>-0.014539168085441733</v>
       </c>
       <c r="P20" s="0">
-        <v>-0.013374409732151153</v>
+        <v>-0.01293391082581862</v>
       </c>
       <c r="Q20" s="0">
-        <v>-0.0092621188952447097</v>
+        <v>-0.0075613978714577593</v>
       </c>
       <c r="R20" s="0">
-        <v>0.72257165518747391</v>
+        <v>0.71763995428992278</v>
       </c>
       <c r="S20" s="0">
-        <v>0.73656407059655682</v>
+        <v>0.73441983505793385</v>
       </c>
       <c r="T20" s="0">
-        <v>0.74782770064660797</v>
+        <v>0.74469346182830398</v>
       </c>
       <c r="U20" s="0">
-        <v>0.0039347395747780624</v>
+        <v>0.0040432526615066392</v>
       </c>
       <c r="V20" s="0">
-        <v>0.0060286983398821917</v>
+        <v>0.0059895888400141569</v>
       </c>
       <c r="W20" s="0">
-        <v>0.0081329874262016239</v>
+        <v>0.008000502778425558</v>
       </c>
       <c r="X20" s="0">
-        <v>-2.7747729580650891</v>
+        <v>-3.5269544995261062</v>
       </c>
       <c r="Y20" s="0">
-        <v>-2.3386719270935301</v>
+        <v>-3.1089148990053896</v>
       </c>
       <c r="Z20" s="0">
-        <v>-1.9025265093759631</v>
+        <v>-2.7142821250515961</v>
       </c>
     </row>
     <row r="21">
@@ -1816,76 +1822,76 @@
       </c>
       <c r="B21" s="0"/>
       <c r="C21" s="0">
-        <v>0.0087168515047231117</v>
+        <v>0.0091212150540263721</v>
       </c>
       <c r="D21" s="0">
-        <v>0.0069028665038693652</v>
+        <v>0.0072106733095521443</v>
       </c>
       <c r="E21" s="0">
-        <v>0.0060789082922248919</v>
+        <v>0.0062304986098959412</v>
       </c>
       <c r="F21" s="0">
-        <v>0.0078049486260683637</v>
+        <v>0.0079175874036791945</v>
       </c>
       <c r="G21" s="0">
-        <v>0.007824907350143016</v>
+        <v>0.0079130590859056299</v>
       </c>
       <c r="H21" s="0">
-        <v>0.0082043518260266034</v>
+        <v>0.0082605991583813154</v>
       </c>
       <c r="I21" s="0">
-        <v>0.011339603807663995</v>
+        <v>0.011412069394378756</v>
       </c>
       <c r="J21" s="0">
-        <v>0.010016157494267328</v>
+        <v>0.0091903502808337884</v>
       </c>
       <c r="K21" s="0">
-        <v>0.010233886289457411</v>
+        <v>0.0083761624542159317</v>
       </c>
       <c r="L21" s="0">
-        <v>0.16728713057568617</v>
+        <v>0.13934819769986012</v>
       </c>
       <c r="M21" s="0">
-        <v>0.15194235808528306</v>
+        <v>0.15382049930699646</v>
       </c>
       <c r="N21" s="0">
-        <v>0.15509583469363711</v>
+        <v>0.12082328543073612</v>
       </c>
       <c r="O21" s="0">
-        <v>0.018579777119205263</v>
+        <v>0.024063554298146054</v>
       </c>
       <c r="P21" s="0">
-        <v>0.019979882401855015</v>
+        <v>0.020975926079235405</v>
       </c>
       <c r="Q21" s="0">
-        <v>0.022720095579814543</v>
+        <v>0.025532386388786889</v>
       </c>
       <c r="R21" s="0">
-        <v>0.1555379816027837</v>
+        <v>0.16562146614665738</v>
       </c>
       <c r="S21" s="0">
-        <v>0.15488592415082145</v>
+        <v>0.15271353260123999</v>
       </c>
       <c r="T21" s="0">
-        <v>0.15761453300720851</v>
+        <v>0.16399816659583696</v>
       </c>
       <c r="U21" s="0">
-        <v>0.0043656675743456649</v>
+        <v>0.0052908932924138176</v>
       </c>
       <c r="V21" s="0">
-        <v>0.0038992086854848515</v>
+        <v>0.0040341199674690971</v>
       </c>
       <c r="W21" s="0">
-        <v>0.0048713239348612417</v>
+        <v>0.0042965780641461924</v>
       </c>
       <c r="X21" s="0">
-        <v>4.2462347927024444</v>
+        <v>5.1602900078734519</v>
       </c>
       <c r="Y21" s="0">
-        <v>3.8398843696073923</v>
+        <v>4.6561801412553727</v>
       </c>
       <c r="Z21" s="0">
-        <v>3.6801705536420646</v>
+        <v>4.3705650376495795</v>
       </c>
     </row>
     <row r="22">
@@ -1923,59 +1929,59 @@
       <c r="B23" s="0"/>
       <c r="C23" s="0"/>
       <c r="D23" s="0">
-        <v>0.017453292341577754</v>
+        <v>0.017453292340025989</v>
       </c>
       <c r="E23" s="0">
-        <v>0.018522425902847764</v>
+        <v>0.0185741107115273</v>
       </c>
       <c r="F23" s="0"/>
       <c r="G23" s="0">
-        <v>-0.00089246004856725263</v>
+        <v>-0.00090829271904408577</v>
       </c>
       <c r="H23" s="0">
-        <v>-0.00081760691989320698</v>
+        <v>-0.00082988978360021574</v>
       </c>
       <c r="I23" s="0"/>
       <c r="J23" s="0">
-        <v>-0.00025909260398586555</v>
+        <v>-0.00028072697570774715</v>
       </c>
       <c r="K23" s="0">
-        <v>-0.00018418111510612949</v>
+        <v>-0.00020226300273406205</v>
       </c>
       <c r="L23" s="0"/>
       <c r="M23" s="0">
-        <v>0.76920491001624714</v>
+        <v>0.76998310610360976</v>
       </c>
       <c r="N23" s="0">
-        <v>0.77125415929144881</v>
+        <v>0.77213345907514441</v>
       </c>
       <c r="O23" s="0"/>
       <c r="P23" s="0">
-        <v>-0.021017233706154482</v>
+        <v>-0.021124587606686125</v>
       </c>
       <c r="Q23" s="0">
-        <v>-0.020769300647921679</v>
+        <v>-0.020864706000723786</v>
       </c>
       <c r="R23" s="0"/>
       <c r="S23" s="0">
-        <v>0.78011109713202209</v>
+        <v>0.77928668674565649</v>
       </c>
       <c r="T23" s="0">
-        <v>0.78264427614600318</v>
+        <v>0.7819404419706123</v>
       </c>
       <c r="U23" s="0"/>
       <c r="V23" s="0">
-        <v>0.0053707625433341132</v>
+        <v>0.0053358968826158039</v>
       </c>
       <c r="W23" s="0">
-        <v>0.0055631306790484931</v>
+        <v>0.0055373322648113984</v>
       </c>
       <c r="X23" s="0"/>
       <c r="Y23" s="0">
-        <v>-2.513849754602596</v>
+        <v>-2.8075709042602006</v>
       </c>
       <c r="Z23" s="0">
-        <v>-2.5091750961885628</v>
+        <v>-2.8026748546948199</v>
       </c>
     </row>
     <row r="24">
@@ -1984,76 +1990,76 @@
       </c>
       <c r="B24" s="0"/>
       <c r="C24" s="0">
-        <v>0.0055528884007337584</v>
+        <v>0.0052413706274960815</v>
       </c>
       <c r="D24" s="0">
-        <v>0.010605451952981071</v>
+        <v>0.010329344159545452</v>
       </c>
       <c r="E24" s="0">
-        <v>0.015140061464171729</v>
+        <v>0.014897562486725011</v>
       </c>
       <c r="F24" s="0">
-        <v>0.0010261388265276807</v>
+        <v>0.0010377115620330574</v>
       </c>
       <c r="G24" s="0">
-        <v>0.0018381763440174785</v>
+        <v>0.001824450869465546</v>
       </c>
       <c r="H24" s="0">
-        <v>0.0027740485158734072</v>
+        <v>0.0027366794734715537</v>
       </c>
       <c r="I24" s="0">
-        <v>-0.0013042385062665355</v>
+        <v>-0.0026488620504586118</v>
       </c>
       <c r="J24" s="0">
-        <v>0.0010694874904584391</v>
+        <v>-0.00033323663188732447</v>
       </c>
       <c r="K24" s="0">
-        <v>0.0034732556324979431</v>
+        <v>0.0019366937493967139</v>
       </c>
       <c r="L24" s="0">
-        <v>0.67165940622396314</v>
+        <v>0.66965213383672906</v>
       </c>
       <c r="M24" s="0">
-        <v>0.71813481150575986</v>
+        <v>0.71547518400735677</v>
       </c>
       <c r="N24" s="0">
-        <v>0.76055896205159967</v>
+        <v>0.75552534373617508</v>
       </c>
       <c r="O24" s="0">
-        <v>-0.017201482949175381</v>
+        <v>-0.016510802220179172</v>
       </c>
       <c r="P24" s="0">
-        <v>-0.01337387347548603</v>
+        <v>-0.013158444397777936</v>
       </c>
       <c r="Q24" s="0">
-        <v>-0.0092618950329389858</v>
+        <v>-0.0089918360145932359</v>
       </c>
       <c r="R24" s="0">
-        <v>0.72274046887294685</v>
+        <v>0.72005986890877261</v>
       </c>
       <c r="S24" s="0">
-        <v>0.73671240121126291</v>
+        <v>0.73391736356211479</v>
       </c>
       <c r="T24" s="0">
-        <v>0.74797505513479035</v>
+        <v>0.7458305207619792</v>
       </c>
       <c r="U24" s="0">
-        <v>0.0039348517021976694</v>
+        <v>0.0035648008365331903</v>
       </c>
       <c r="V24" s="0">
-        <v>0.0060288785224047094</v>
+        <v>0.0055879841189357491</v>
       </c>
       <c r="W24" s="0">
-        <v>0.0081331734303132699</v>
+        <v>0.0076118748272202413</v>
       </c>
       <c r="X24" s="0">
-        <v>-2.773991341534721</v>
+        <v>-3.5283201564228541</v>
       </c>
       <c r="Y24" s="0">
-        <v>-2.3374388452933581</v>
+        <v>-3.1082010592799478</v>
       </c>
       <c r="Z24" s="0">
-        <v>-1.9013256457841123</v>
+        <v>-2.7141202254446375</v>
       </c>
     </row>
     <row r="25">
@@ -2062,76 +2068,76 @@
       </c>
       <c r="B25" s="0"/>
       <c r="C25" s="0">
-        <v>0.0087168529804736387</v>
+        <v>0.0090490374019946852</v>
       </c>
       <c r="D25" s="0">
-        <v>0.0069029143224545427</v>
+        <v>0.0072108339283008475</v>
       </c>
       <c r="E25" s="0">
-        <v>0.0060791287160926041</v>
+        <v>0.0062704297227428058</v>
       </c>
       <c r="F25" s="0">
-        <v>0.007804960141233541</v>
+        <v>0.0079161589754811277</v>
       </c>
       <c r="G25" s="0">
-        <v>0.0078249119080905857</v>
+        <v>0.0079116949988194806</v>
       </c>
       <c r="H25" s="0">
-        <v>0.0082043656381939854</v>
+        <v>0.0082565033832889198</v>
       </c>
       <c r="I25" s="0">
-        <v>0.011339781046632656</v>
+        <v>0.011393377369439121</v>
       </c>
       <c r="J25" s="0">
-        <v>0.010016428336187756</v>
+        <v>0.0091768509217846385</v>
       </c>
       <c r="K25" s="0">
-        <v>0.010234205906037012</v>
+        <v>0.00836101164218476</v>
       </c>
       <c r="L25" s="0">
-        <v>0.16702043935905356</v>
+        <v>0.17576447604817408</v>
       </c>
       <c r="M25" s="0">
-        <v>0.15125155257062109</v>
+        <v>0.15298328850605947</v>
       </c>
       <c r="N25" s="0">
-        <v>0.15410835196270575</v>
+        <v>0.15951238725316794</v>
       </c>
       <c r="O25" s="0">
-        <v>0.018581030928438075</v>
+        <v>0.019761461363262456</v>
       </c>
       <c r="P25" s="0">
-        <v>0.019979979850443634</v>
+        <v>0.020690380339104156</v>
       </c>
       <c r="Q25" s="0">
-        <v>0.022720037278922658</v>
+        <v>0.023508162054298867</v>
       </c>
       <c r="R25" s="0">
-        <v>0.15471004003628186</v>
+        <v>0.1534904496024867</v>
       </c>
       <c r="S25" s="0">
-        <v>0.15414366266985652</v>
+        <v>0.1552400346568292</v>
       </c>
       <c r="T25" s="0">
-        <v>0.15687535690236504</v>
+        <v>0.15618262815752193</v>
       </c>
       <c r="U25" s="0">
-        <v>0.0043656705611639975</v>
+        <v>0.004897110092862398</v>
       </c>
       <c r="V25" s="0">
-        <v>0.0038991476913658035</v>
+        <v>0.0039061154320263261</v>
       </c>
       <c r="W25" s="0">
-        <v>0.0048712020913790335</v>
+        <v>0.0043102573960231323</v>
       </c>
       <c r="X25" s="0">
-        <v>4.2463764034695633</v>
+        <v>5.154757373466996</v>
       </c>
       <c r="Y25" s="0">
-        <v>3.8398626242755922</v>
+        <v>4.6504237502784802</v>
       </c>
       <c r="Z25" s="0">
-        <v>3.6800300404491875</v>
+        <v>4.3646302889951034</v>
       </c>
     </row>
     <row r="26">
